--- a/output/OR202605280844126040_alternate_purchases.xlsx
+++ b/output/OR202605280844126040_alternate_purchases.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Alternate Purchase Recommendations  ·  Ref: OR202605280844126040  ·  Generated: 2026-06-25 07:20  ·  Items here do NOT appear in the Price Match report</t>
+          <t>Alternate Purchase Recommendations  ·  Ref: OR202605280844126040  ·  Generated: 2026-06-25 22:54  ·  Items here do NOT appear in the Price Match report</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -952,5689 +952,5714 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx
+SKU: 1126830  ·  Schein price: $16.15/unit</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Criterion N300 Nitrile Exam Gloves – Standard Ice Blue, Non-Sterile – For Medical, Exam &amp; General Use - Small, BX/300</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>suprememed.com</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>https://www.suprememed.com/criterion-n300-nitrile-exam-gloves-standard-ice-blue-non-sterile/?attribute_pa_unit-of-measure-conf=bx300&amp;attribute_pa_size-conf=small</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>EXACT — same product, different brand or channel; substitution is straightforward
+Web search (not in Price Match) · EXACT (98%) · Matching: brand, product name, form/spec, pack size · The page explicitly states 'Size: Small' and 'Unit of Measure BX/300' and the product name includes 'Ice Blue, Non-Sterile - Small, BX/300'. The manufacturer part number 1126830 is listed, which is different from the ordered MPN 5703541. However, the original description 'Criterion N300 Glove Ice Blue Nitrile S 300/Bx' matches the product name and variant on the page. Given the brand, product name, variant, and pack quantity match, and the MPN is a Henry Schein number (as per page 0), this is considered an exact match despite the MPN difference, as the product itself appears to be the same.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Equiv $16.61 &gt; Schein $16.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Criterion N300 Glove Ice Blue Nitrile M 300/Bx
+SKU: 1126831  ·  Schein price: $16.15/unit</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Criterion N300 Nitrile Exam Gloves Medium Standard Ice Blue Non-Sterile Chemo Tested</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>acesouthern.com</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>35.79</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>https://www.acesouthern.com/product/criterion-nitrile-n300-glv-1126831</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>EXACT — same product, different brand or channel; substitution is straightforward
+Web search (not in Price Match) · EXACT (98%) · Matching: brand, product name, form/spec, pack size</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Equiv $35.79 &gt; Schein $16.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Floss Deep Clean 4 meter Mint 72/Bx
+SKU: 3250498  ·  Schein price: $50.99/unit</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Deep Clean Floss</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>sourceonedental.com</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>https://sourceonedental.com/product/oral-b-glide-deep-clean-floss/173306</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>EXACT (99%)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>EXACT — same product, different brand or channel; substitution is straightforward
+Web search (not in Price Match) · EXACT (99%) · Matching: brand, product name, form/spec, pack size · price $51.99 from page structured data (single offer) · Exact match found, including MPN 80779741.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Equiv $51.99 &gt; Schein $50.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
           <t>Sharps Cont Counter Balanced 3 Gal RD Ea
 SKU: 9872474  ·  Schein price: $17.42/unit</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Counterbalanced Door Sharps Collectors by BD</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>graylinemedical.com</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D15" s="11" t="n">
         <v>27.99</v>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>https://www.graylinemedical.com/products/counterbalanced-door-sharps-collectors-by-bd</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>EXACT (98%)</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>EXACT — same product, different brand or channel; substitution is straightforward
 Web search (not in Price Match) · EXACT (98%) · Matching: brand, product name, form/spec, pack size · Matched by MPN, size, and color.</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Equiv $27.99 &gt; Schein $17.42</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ReSURGE Inst Cleaning Solution 33oz/Bt
+SKU: 3120114  ·  Schein price: $91.15/unit</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>RESURGE INSTRUMENT CLEANING SOLUTION</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>newarkdentalpemco.com</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>105.39</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>https://newarkdentalpemco.com/products/resurge-inst-cleaning-solution</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>EXACT (98%)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>EXACT — same product, different brand or channel; substitution is straightforward
+Web search (not in Price Match) · EXACT (98%) · Matching: brand, product name, form/spec, pack size · variant-matrix price $105.39 (ordered variant by size/title: Bottle 33oz) · Price extracted for 'Bottle 33oz' variant.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Equiv $105.39 &gt; Schein $91.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
 SKU: 1403081  ·  Schein price: $9.59/unit</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Large 160/Can</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D17" s="11" t="n">
         <v>10.08</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/CaviWipes-2.0-14-1100_2</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>EXACT (98%)</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>EXACT — same product, different brand or channel; substitution is straightforward
 Web search (not in Price Match) · EXACT (98%) · Matching: brand, product name, form/spec, pack size · Price extracted from 'Our Price' and confirmed by Net32 price. The product name on the page is 'CaviWipes 2.0 Large 160/Can', which matches the ordered product family and pack quantity. The MPN 14-1100 is also present in the SKU.</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Equiv $10.08 &gt; Schein $9.59</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="64" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
 SKU: 1403081  ·  Schein price: $9.59/unit</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>CaviWipes 2.0</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>pearsondental.com</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n">
+      <c r="D18" s="7" t="n">
         <v>13.9</v>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>https://www.pearsondental.com/catalog/product.asp?majcatid=15349&amp;catid=10781&amp;subcatid=41275&amp;pid=98008</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>EXACT (99%)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>EXACT — same product, different brand or channel; substitution is straightforward
 Web search (not in Price Match) · EXACT (99%) · Matching: brand, product name, form/spec, pack size · Matched 'CaviWipes 2.0 6"x6.75" Canister of 160' with Mfg. Part # 14-1100-EA. The ordered MPN was 14-1100, which is a close match.</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Equiv $13.90 &gt; Schein $9.59</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
 SKU: 1403081  ·  Schein price: $9.59/unit</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Disinfectant Wipes 6'x 6.75', 160/Can. Enhanced Efficacy</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>thedentalmarket.net</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D19" s="11" t="n">
         <v>16.95</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>https://thedentalmarket.net/featured-items/caviwipes-2-0-disinfectant-wipes-6x-6-75-160-can-enhanced-efficacy/</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>EXACT (98%)</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>EXACT — same product, different brand or channel; substitution is straightforward
 Web search (not in Price Match) · EXACT (98%) · Matching: brand, product name, form/spec, pack size</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Equiv $16.95 &gt; Schein $9.59</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="64" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Diamond FG Coarse 841G-012 5/Pk
 SKU: 7011085  ·  Schein price: $43.65/unit</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Meisinger Diamond Cylinder Round Edge 841G Coarse</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>chasedentalsupply.com</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D20" s="7" t="n">
         <v>43.88</v>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>https://chasedentalsupply.com/meisinger-diamond-cylinder-round-edge-841g-coarse/</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>EXACT (98%)</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>EXACT — same product, different brand or channel; substitution is straightforward
 Web search (not in Price Match) · EXACT (98%) · Matching: brand, product name, form/spec, pack size · Exact match for variant and pack quantity. MPN 841G-012-FG is present.</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Equiv $43.88 &gt; Schein $43.65</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk
 SKU: 8889527  ·  Schein price: $71.70/unit</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Coltene ParaPost Fiber Lux</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>ansondental.com</t>
         </is>
       </c>
-      <c r="D17" s="15" t="n">
+      <c r="D21" s="15" t="n">
         <v>49.99</v>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>https://ansondental.com/products/coltene-parapost-fiber-lux?currency=USD&amp;country=US&amp;variant=40281234505862&amp;stkn=84caddec0854</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>APPROXIMATE (98%)</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (98%) · Matching: brand, product name, form/spec, pack size · Price found for the exact ordered variant and pack quantity. · OUT OF STOCK / no longer available on this page — not a buyable price; shown for reference only, VERIFY availability</t>
         </is>
       </c>
-      <c r="H17" s="15" t="n">
+      <c r="H21" s="15" t="n">
         <v>21.71</v>
       </c>
     </row>
-    <row r="18" ht="64" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk
 SKU: 8889527  ·  Schein price: $71.70/unit</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Coltene - ParaPost Fiber Lux</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>dentalcity.com</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
+      <c r="D22" s="7" t="n">
         <v>93.37</v>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>https://www.dentalcity.com/product/1588/coltene-parapost-fiber-lux</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Red)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, form/spec, pack size · Not matching: product name · Ordered variant 'Red' but page sells '#5'. MPN PF1715 matches.</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>Equiv $93.37 &gt; Schein $71.70</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="64" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Mity K-Files 25mm #10 6/Pk
 SKU: 2013820  ·  Schein price: $25.40/unit</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Kerr Endodontics K-Files 25mm #10 6/Box.</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D19" s="15" t="n">
+      <c r="D23" s="15" t="n">
         <v>10.65</v>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/sybronendo-kfiles-25mm-10-6-stainless-steel-d-26642</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>APPROXIMATE (20%)</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 6 vs ordered 6) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: #10 25mm)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (20%) · Not matching: brand, product name, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 12 seller(s), via Lowest Price row · Price requires login or is not publicly displayed. Brand 'Kerr Endodontics' differs from ordered 'Dentsply Sirona'. Product name 'Kerr Endodontics K-Files' differs from ordered 'Mity K-Files'. · kept despite a login note — aggregator shows a public price; VERIFY the in-cart total</t>
         </is>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H23" s="15" t="n">
         <v>14.75</v>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Mity K-Files 25mm #10 6/Pk
 SKU: 2013820  ·  Schein price: $25.40/unit</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Mity K-Files NT 25mm #10 6/pk</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D24" s="15" t="n">
         <v>22.3</v>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/mity-k-files-nt-25mm-10-6-pk-js-2k5010</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>APPROXIMATE (20%)</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 6 vs ordered 6) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: #10 25mm)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (20%) · Not matching: brand, product name, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 1 seller(s), via min of Total column · Price requires login or is not publicly displayed. Product name 'Mity K-Files NT' differs from ordered 'Mity K-Files'. · kept despite a login note — aggregator shows a public price; VERIFY the in-cart total</t>
         </is>
       </c>
-      <c r="H20" s="15" t="n">
+      <c r="H24" s="15" t="n">
         <v>3.1</v>
       </c>
     </row>
-    <row r="21" ht="64" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Cranberry® S3+ ASTM Level 3 Face Masks 50/Box</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>practicon.com</t>
         </is>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D25" s="11" t="n">
         <v>11.69</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>https://www.practicon.com/cranberry-s3-astm-level-3-face-masks/p/70183103</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: product name, form/spec, pack size · Not matching: brand · Brand mismatch (Cranberry vs Henry Schein).</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>Equiv $11.69 &gt; Schein $9.55</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="64" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>S3+ EARLOOP FACE MASKS LEVEL 3 (50/BX)</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>newarkdentalpemco.com</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D26" s="7" t="n">
         <v>16.99</v>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>https://newarkdentalpemco.com/products/face-masks-s3-white-50-bx</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (94%)</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: L3 Black)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (94%) · Matching: brand, product name, form/spec, pack size · PRICE UNRELIABLE — extracted $16.99 does not appear on the scraped page; likely a related-item or mis-read price, VERIFY MANUALLY · Page sells 'White' variant, buyer ordered 'L3 Black'. MPN S3160K matches.</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>Equiv $16.99 &gt; Schein $9.55</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk
 SKU: 2222660  ·  Schein price: $76.60/unit</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>Top Quality Dynamic Mixing Tips Yellow</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>topqualitygloves.com</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D27" s="15" t="n">
         <v>22.25</v>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>https://topqualitygloves.com/products/top-quality-dynamic-mixing-tips-yellow?variant=39836793995335&amp;ab_version=A&amp;com_cvv=8fb3d522dc163aeadb66e08cd7450cbbdddc64c6cf2e8891f6d48747c6d56d2c</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F27" s="14" t="inlineStr">
         <is>
           <t>APPROXIMATE (58%)</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 50 vs ordered 40)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (58%) · Matching: product name, form/spec · Not matching: brand, pack size · Brand is 'Top Quality Manufacturing' not 'Kulzer'. Pack quantity is 50, not 40. Variant is 'Yellow' but does not specify 'w/LuerLock'. · PACK MISMATCH — page is 50/pack but ordered 40/pack; treated as approximate, VERIFY · PRICE UNRELIABLE — $22.25 is far below the other sources for this item (median $60.91); likely a related-item or single-unit price, VERIFY MANUALLY</t>
         </is>
       </c>
-      <c r="H23" s="15" t="n">
+      <c r="H27" s="15" t="n">
         <v>54.35</v>
       </c>
     </row>
-    <row r="24" ht="64" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="28" ht="64" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Genie VPS Magic Mix Stand Bulk Heavy Body 4/Pk
 SKU: 3120199  ·  Schein price: $518.89/unit</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>Sultan - Genie Magic Mix</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>dentalcity.com</t>
         </is>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D28" s="15" t="n">
         <v>194.39</v>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>https://www.dentalcity.com/product/11616/sultan-genie-magic-mix</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F28" s="14" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 1 vs ordered 4)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
-Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, product name, form/spec · Not matching: pack size · The page sells a single 380mL cartridge, not a 4-pack. The variant 'Heavy Body Standard Set' is present, but the pack quantity is a mismatch. · PACK MISMATCH — page is 1/pack but ordered 4/pack; treated as approximate, VERIFY</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n">
+Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, product name, form/spec · Not matching: pack size · The page sells a single 380mL cartridge, not a 4-pack. The variant 'Heavy Body Standard Set' is present, but the pack quantity is a mismatch. · PACK MISMATCH — page is 1/pack but ordered 4/pack; treated as approximate, VERIFY · PRICE UNRELIABLE — $194.39 is far below the other sources for this item (median $495.95); likely a related-item or single-unit price, VERIFY MANUALLY</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
         <v>324.5</v>
       </c>
     </row>
-    <row r="25" ht="64" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Genie VPS Magic Mix Stand Bulk Heavy Body 4/Pk
 SKU: 3120199  ·  Schein price: $518.89/unit</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>GENIE VPS Magic Mix 380mL Heavy Body Standard Set 4/Pk</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D29" s="11" t="n">
         <v>534.49</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Genie-VPS-78835</t>
         </is>
       </c>
-      <c r="F25" s="10" t="inlineStr">
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (96%)</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (96%) · Matching: brand, product name, form/spec, pack size · The product name includes 'Standard Set' which was not specified in the order, but is a common variant for this product line. The pack quantity matches.</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>Equiv $534.49 &gt; Schein $518.89</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="64" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Genie Putty Rapid Set Berry 2x445 Gr
 SKU: 3122330  ·  Schein price: $121.60/unit</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>GENIE Putty Rapid Set 2 × 300 mL Berry (77650) – Berry‑Flavored VPS Impression Putty, Rapid Set (Sultan/Dentsply)</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>acmedent.com</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D30" s="7" t="n">
         <v>126.4</v>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>https://www.acmedent.com/products/28585</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (81%)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (81%) · Matching: brand, product name, pack size · Not matching: form/spec · Product name and variant match, but the size/form is 2x300 mL, not 2x445 Gr as ordered. The product is also sold out. · OUT OF STOCK / no longer available on this page — not a buyable price; shown for reference only, VERIFY availability</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>Equiv $126.40 &gt; Schein $121.60</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="64" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Speedclean For Autoclave 16oz/Bt
 SKU: 3865728  ·  Schein price: $35.99/unit</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Speed-Clean Autoclave Cleaner</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>lexiconsupply.com</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D31" s="15" t="n">
         <v>20.99</v>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>https://www.lexiconsupply.com/products/speed-clean-autoclave-cleaner?variant=43064821448740&amp;country=US&amp;currency=USD</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: product name, form/spec, pack size · Not matching: brand · Brand mismatch (Lexicon Medical Supply vs SciCan). Product is out of stock. MPN 002-0396-05 matches ordered MPN 002039605. · OUT OF STOCK / no longer available on this page — not a buyable price; shown for reference only, VERIFY availability</t>
         </is>
       </c>
-      <c r="H27" s="15" t="n">
+      <c r="H31" s="15" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="28" ht="64" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9736H-150 2/Pk
 SKU: 7013176  ·  Schein price: $66.58/unit</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Meisinger Mounted Polisher Extra Coarse Black / Orange Refill 2/Pk</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>amtouch.com</t>
         </is>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D32" s="7" t="n">
         <v>67.2</v>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>https://www.amtouch.com/shop-by-category/finishing-polishing/meisinger-mounted-polisher-extra-coarse-black-orange-refill-2-pk/</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: specified)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, form/spec, pack size · Not matching: product name · Product name indicates 'Mounted Polisher Extra Coarse Black / Orange' which is a specific variant, while the order was for 'Polisher HP' with no specific variant. MPN is not explicitly stated on the page to confirm exact match, but the ordered MPN 9736H-150-HP-TRQ is not present in the product title or description.</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>Equiv $67.20 &gt; Schein $66.58</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="64" customHeight="1">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9736H-150 2/Pk
 SKU: 7013176  ·  Schein price: $66.58/unit</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>TRQ Abrasive, Turquoise, Wheel, Diamond Porcelain for Ceramics, Zirconia Sprue Removal, 15mm Ø, Coarse, HP - 9736H-150-HP</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>avtecdental.com</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D33" s="11" t="n">
         <v>75.25</v>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>https://www.avtecdental.com/products/trq-abrasive-turquoise-wheel-diamond-porcelain-for-ceramics-zirconia-sprue-removal-15mm-o-coarse-hp-9736h-150-hp</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (81%)</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered 2)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (81%) · Matching: brand, product name, form/spec · Not matching: pack size · Pack quantity not specified on page, assuming 1. Ordered pack quantity is 2.</t>
         </is>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Equiv $75.25 &gt; Schein $66.58</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="64" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
 SKU: 7120116  ·  Schein price: $13.35/unit</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>GUM Technique Deep Clean Adult Soft Manual Toothbrushes, 12/Pack</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>safcodental.com</t>
         </is>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D34" s="7" t="n">
         <v>14.49</v>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/product/gum-technique-deep-clean-adult-soft-toothbrushes</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (96%)</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (96%) · Matching: brand, product name, form/spec, pack size · Variant is 'Soft' instead of 'Soft Compact'. Assuming 'Soft' is the same as 'Soft Compact' for this product line.</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>Equiv $14.49 &gt; Schein $13.35</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
 SKU: 7120116  ·  Schein price: $13.35/unit</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Toothbrush GUM Technique Sensitive Care Compact 12/Bx</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D35" s="11" t="n">
         <v>14.49</v>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Technique-Sensitive-Care-517PG</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Soft Compact)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, form/spec, pack size · Not matching: product name · Product name is 'Sensitive Care Compact' instead of 'Deep Clean Soft Compact'. MPN 681-517PG does not match ordered 524TPA1.</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>Equiv $14.49 &gt; Schein $13.35</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="64" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
 SKU: 7120116  ·  Schein price: $13.35/unit</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>GUM Technique Deep Clean Manual Toothbrush Adult Sensitive Compact 12/Bx</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>dentalwholesaledirect.com</t>
         </is>
       </c>
-      <c r="D32" s="7" t="n">
+      <c r="D36" s="7" t="n">
         <v>17.95</v>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>https://dentalwholesaledirect.com/preventives/gum-technique-deep-clean-manual-toothbrush-adult-sensitive-compact-12-bx/</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Soft Compact)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, form/spec, pack size · Not matching: product name · Product variant is 'Sensitive Compact' instead of 'Soft Compact'. MPN 527TPA1 does not match ordered 524TPA1.</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Equiv $17.95 &gt; Schein $13.35</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="64" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
 SKU: 7120116  ·  Schein price: $13.35/unit</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>GUM Technique Deep Clean Toothbrush - Compact Head, Sensitive 12/Pk. Bi-Level</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D37" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/gum-technique-deep-clean-toothbrush-compact-head-d-133050</t>
         </is>
       </c>
-      <c r="F33" s="10" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (88%)</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (88%) · Matching: brand, product name, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 2 seller(s), via Lowest Price row · Price requires login. Variant 'Sensitive Compact Head Bi-Level' does not match 'Soft Compact'. · kept despite a login note — aggregator shows a public price; VERIFY the in-cart total</t>
         </is>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Equiv $19.00 &gt; Schein $13.35</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="64" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
 SKU: 7120116  ·  Schein price: $13.35/unit</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>GUM Technique Deep Clean Toothbrush - Compact Head, Soft Bristles 12/Pk</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D34" s="7" t="n">
+      <c r="D38" s="7" t="n">
         <v>22.85</v>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/gum-technique-deep-clean-toothbrush-compact-head-d-133049</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (92%)</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (92%) · Matching: brand, product name, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 3 seller(s), via Lowest Price row · Price requires login. Variant 'Soft Bristles Compact Head' is a close match to 'Soft Compact'.</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Equiv $22.85 &gt; Schein $13.35</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="64" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk
 SKU: 7772551  ·  Schein price: $278.99/unit</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>Clinpro Clear 2.1% Sodium Fluoride Treatment, 0.5 mL Unit Dose, Watermelon Flavor, 100/Pk</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D39" s="15" t="n">
         <v>240.9</v>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/clinpro-clear-21-sodium-fluoride-treatment-05-d-182709</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>APPROXIMATE (77%)</t>
         </is>
       </c>
-      <c r="G35" s="13" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: No Flavor)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (77%) · Matching: brand, form/spec, pack size · Not matching: product name · price set from net32.com seller table: lowest available (incl. shipping) of 2 seller(s), via Lowest Price row · Price requires login. Variant (Watermelon) does not match ordered (No Flavor). · VARIANT MISMATCH — flavor mismatch (ordered 'no flavor', page 'watermelon'); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H39" s="15" t="n">
         <v>38.09</v>
       </c>
     </row>
-    <row r="36" ht="64" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk
 SKU: 7772551  ·  Schein price: $278.99/unit</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Clinpro Clear Fluoride Treatment</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>amtouch.com</t>
         </is>
       </c>
-      <c r="D36" s="7" t="n">
+      <c r="D40" s="7" t="n">
         <v>288.27</v>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>https://www.amtouch.com/shop-by-category/preventives/clinpro-clear-fluoride-treatment/</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (73%)</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered 100) · VARIANT MISMATCH (ordered: No Flavor)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
-Web search (not in Price Match) · APPROXIMATE (73%) · Matching: brand, product name, form/spec · Not matching: pack size · variant-matrix price $288.27 (page SKU 3M-7210FF == order MPN 7210FF) · Pack quantity and variant not explicitly stated for the priced item, but the product name matches. The price range suggests multiple options, but only a base price is extractable without specific variant selection.</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
+Web search (not in Price Match) · APPROXIMATE (73%) · Matching: brand, product name, form/spec · Not matching: pack size · variant-matrix price $288.27 (ordered variant by SKU/MPN: 3M-7210FF) · Pack quantity and variant not explicitly stated for the priced item, but the product name matches. The price range suggests multiple options, but only a base price is extractable without specific variant selection.</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>Equiv $288.27 &gt; Schein $278.99</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="64" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
 SKU: 1024081  ·  Schein price: $28.89/unit</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>Tray Covers, Ritter, # B, 8.5" x 12.25", Blue, 1000/Pk - HSB House Brand Dentistry</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D41" s="15" t="n">
         <v>17.65</v>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/tray-covers-ritter-b-8-5-x-12-25-blue-1000-pk-hsb-house-brand-dentistry-101130</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>APPROXIMATE (65%)</t>
         </is>
       </c>
-      <c r="G37" s="13" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Aqua)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (65%) · Matching: brand, form/spec, pack size · Not matching: product name · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 1 seller(s), via min of Total column · Price not found on page. Product name from URL/title. Variant is Blue, not Aqua. · VARIANT MISMATCH — color mismatch (ordered aqua, page blue); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H37" s="15" t="n">
+      <c r="H41" s="15" t="n">
         <v>11.24</v>
       </c>
     </row>
-    <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
 SKU: 1024081  ·  Schein price: $28.89/unit</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Paper Tray Covers Size B 8.5" x 12.25"(Ritter) 1000/Bx Blue</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D42" s="7" t="n">
         <v>28.2</v>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Paper-Tray-Covers-PAP-B2</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Aqua)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, form/spec, pack size · Not matching: product name · Variant color mismatch (Blue vs Aqua). · VARIANT MISMATCH — color mismatch (ordered aqua, page blue); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H42" s="7" t="n">
         <v>0.6899999999999999</v>
       </c>
     </row>
-    <row r="39" ht="64" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
 SKU: 1024081  ·  Schein price: $28.89/unit</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Posi-Guard™ Tray Cover 8.5"x 12.25", 1000 Per Box</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>clinicalsupplycompany.com</t>
         </is>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D43" s="11" t="n">
         <v>33.5</v>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>https://clinicalsupplycompany.com/products/posi-guard-tray-cover-8-5x-12-25-1000-per-box</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (81%)</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Aqua)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (81%) · Matching: product name, form/spec, pack size · Not matching: brand · Brand mismatch (Posi-Guard vs None). Variant mismatch (Blue vs Aqua). · VARIANT MISMATCH — color mismatch (ordered aqua, page blue); wrong variant, routed to alternate, VERIFY · OUT OF STOCK / no longer available on this page — not a buyable price; shown for reference only, VERIFY availability</t>
         </is>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>Equiv $33.50 &gt; Schein $28.89</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="64" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
 SKU: 1024081  ·  Schein price: $28.89/unit</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Tray Covers 8.5" x 12.25", Blue, 1000/Pack | Disposable Tray Liners, 3BS Dahabi (House Brand)</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>3bsdahabicompany.com</t>
         </is>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D44" s="7" t="n">
         <v>33.9</v>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>https://3bsdahabicompany.com/products/tray-cover-1000-box-blue</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Aqua)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, form/spec, pack size · Not matching: product name · Variant color is Blue, but ordered was Aqua. Brand is 3BS Dahabi (House Brand), ordered was None (generic). · VARIANT MISMATCH — color mismatch (ordered aqua, page blue); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>Equiv $33.90 &gt; Schein $28.89</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="64" customHeight="1">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
 SKU: 1024081  ·  Schein price: $28.89/unit</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Tray Cover - 8.5"x12.25" (1000/box)</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>smilestreamsolutions.com</t>
         </is>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D45" s="11" t="n">
         <v>35.27</v>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>https://smilestreamsolutions.com/products/tray-cover-8-5x12-25</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (88%)</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Aqua)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (88%) · Matching: brand, product name, form/spec, pack size · Variant (color) is not specified on the page, but other attributes match.</t>
         </is>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>Equiv $35.27 &gt; Schein $28.89</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="64" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
 SKU: 1024081  ·  Schein price: $28.89/unit</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Crosstex - Tray Cover Size B Aqua 1000/Cs</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>carolinadental.com</t>
         </is>
       </c>
-      <c r="D42" s="7" t="n">
+      <c r="D46" s="7" t="n">
         <v>37.12</v>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
         <is>
           <t>https://carolinadental.com/products/crosstex-tray-cover-size-b-aqua-1000-cs</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (64%)</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (64%) · Matching: product name, pack size · Not matching: brand, form/spec · Brand mismatch (Crosstex vs None). Size 'Size B' is not '8.5"x12.25"'. · OUT OF STOCK / no longer available on this page — not a buyable price; shown for reference only, VERIFY availability</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>Equiv $37.12 &gt; Schein $28.89</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="64" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx
+SKU: 1126830  ·  Schein price: $16.15/unit</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Criterion N300 Nitrile Exam Gloves, Small, Electric Blue</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>acesouthern.com</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>https://www.acesouthern.com/product/criterion-n300-nitrile-exam-gloves-small-electric-blue-5703541</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (96%)</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (96%) · Matching: brand, product name, form/spec, pack size · Variant color 'Electric Blue' does not match ordered 'Ice Blue'. MPN 5703541 matches.</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Equiv $31.99 &gt; Schein $16.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Criterion N300 Glove Ice Blue Nitrile M 300/Bx
+SKU: 1126831  ·  Schein price: $16.15/unit</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Criterion N300 Nitrile Exam Gloves, Large, Electric Blue</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>acesouthern.com</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>https://www.acesouthern.com/product/criterion-n300-nitrile-exam-gloves-large-electric-blue-5703543</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (96%)</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (96%) · Matching: brand, product name, form/spec, pack size · Variant mismatch: ordered 'Ice Blue Medium', page sells 'Electric Blue Large'.</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Equiv $31.99 &gt; Schein $16.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9742M-040 2/Pk
 SKU: 7013185  ·  Schein price: $47.55/unit</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>Polisher, Diamond Impregnated, For Porcelain, Blue / Orange, Point, 4mm Ø, Polishing (Medium), HP - 9742M-040-HP-BL / O</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
         <is>
           <t>avtecdental.com</t>
         </is>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D49" s="11" t="n">
         <v>45.5</v>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>https://www.avtecdental.com/products/polisher-diamond-impregnated-for-porcelain-blue-orange-point-4mm-o-polishing-medium-hp-9742m-040-hp-bl-o-1?currency=USD&amp;country=US&amp;variant=47172801102049&amp;stkn=3211f317f567</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (83%)</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 1 vs ordered 2)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (83%) · Matching: brand, product name, form/spec · Not matching: pack size · Pack quantity mismatch. Ordered 2, page sells 1. MPN matches. · PACK MISMATCH — page is 1/pack but ordered 2/pack; treated as approximate, VERIFY</t>
         </is>
       </c>
-      <c r="H43" s="11" t="n">
+      <c r="H49" s="11" t="n">
         <v>2.05</v>
       </c>
     </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="50" ht="64" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Floss Deep Clean 4 meter Mint 72/Bx
+SKU: 3250498  ·  Schein price: $50.99/unit</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Deep Clean Floss 15m Mint 72/Cs</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>crazydentalprices.com</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>78.48999999999999</v>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Oral-B-Glide-Floss-80775876</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (81%)</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page
+CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (81%) · Matching: brand, product name, pack size · Not matching: form/spec · Product size is 15m, ordered 4m.</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Equiv $78.49 &gt; Schein $50.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="64" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Sharps Cont Counter Balanced 3 Gal RD Ea
 SKU: 9872474  ·  Schein price: $17.42/unit</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>BD Patient Room Sharps Collectors with Counterbalanced Door - Patient Room Sharps Collector with Counterbalanced Door, Red, 3 gal. - 305436</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>graylinemedical.com</t>
         </is>
       </c>
-      <c r="D44" s="7" t="n">
+      <c r="D51" s="11" t="n">
         <v>31.99</v>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr">
         <is>
           <t>https://www.graylinemedical.com/products/bd-patient-room-sharps-collectors-with-counterbalanced-door-patient-room-sharps-collector-with-counterbalanced-door-red-3-gal-305436</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (98%)</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (98%) · Matching: brand, product name, form/spec, pack size · Product is out of stock. · OUT OF STOCK / no longer available on this page — not a buyable price; shown for reference only, VERIFY availability</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>Equiv $31.99 &gt; Schein $17.42</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="64" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="52" ht="64" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>ReSURGE Inst Cleaning Solution 33oz/Bt
 SKU: 3120114  ·  Schein price: $91.15/unit</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>ReSURGE Instrument Cleaning Solution 33 oz 33oz/Bt</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D52" s="7" t="n">
         <v>104.64</v>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/resurge-instrument-cleaning-solution-33-oz-33oz-bt-dentsply-sirona-21521</t>
         </is>
       </c>
-      <c r="F45" s="10" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (80%)</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (80%) · Matching: brand, product name, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 1 seller(s), via min of Total column · Price not found on page, only descriptive text about buy box algorithm.</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Equiv $104.64 &gt; Schein $91.15</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="64" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="53" ht="64" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>ReSURGE Inst Cleaning Solution 33oz/Bt
 SKU: 3120114  ·  Schein price: $91.15/unit</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>ReSURGE Instrument Cleaning Solution</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>purelifedental.com</t>
         </is>
       </c>
-      <c r="D46" s="7" t="n">
+      <c r="D53" s="11" t="n">
         <v>112.99</v>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr">
         <is>
           <t>https://www.purelifedental.com/resurge-instrument-cleaning-solution.html</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (99%)</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (99%) · Matching: brand, product name, form/spec, pack size · Matched 33.8oz bottle (closest to 33oz) with MPN 21521. · OUT OF STOCK / no longer available on this page — not a buyable price; shown for reference only, VERIFY availability</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>Equiv $112.99 &gt; Schein $91.15</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="64" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
+    <row r="54" ht="64" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
 SKU: 1403081  ·  Schein price: $9.59/unit</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Disinfectant Wipes 6"x 6.75", 160/Can</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D54" s="7" t="n">
         <v>10.11</v>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/caviwipes-20-disinfectant-wipes-6x675-160-enhanced-d-170013</t>
         </is>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (88%)</t>
         </is>
       </c>
-      <c r="G47" s="9" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (88%) · Matching: brand, product name, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 18 seller(s), via Lowest Price row · Price requires login.</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>Equiv $10.11 &gt; Schein $9.59</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="64" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="55" ht="64" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
         <is>
           <t>Fuji II LC Capsules A3.5 48/Bx
 SKU: 3333468  ·  Schein price: $372.66/unit</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>GC Fuji II LC A3.5 capsules 50/Pk. EXPORT PACKAGE. Light-Cure Resin Reinforced</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>net32.com</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>299.95</v>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/gc-fuji-ii-lc-a35-capsules-50-d-20091</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (77%)</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 50 vs ordered 48)
+CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (77%) · Matching: brand, product name, form/spec · Not matching: pack size · price set from net32.com seller table: lowest available (incl. shipping) of 1 seller(s), via Lowest Price row · Price requires login. Pack quantity is 50, not 48. · PACK MISMATCH — page is 50/pack but ordered 48/pack; treated as approximate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>72.70999999999999</v>
+      </c>
+    </row>
+    <row r="56" ht="64" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>Fuji II LC Capsules A3.5 48/Bx
+SKU: 3333468  ·  Schein price: $372.66/unit</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
         <is>
           <t>Fuji II - LC Capsules A3 48/Bx</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>carolinadental.com</t>
         </is>
       </c>
-      <c r="D48" s="15" t="n">
+      <c r="D56" s="15" t="n">
         <v>312.41</v>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="E56" s="16" t="inlineStr">
         <is>
           <t>https://carolinadental.com/products/fuji-ii-lc-capsules-a3-48-bx</t>
         </is>
       </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="F56" s="14" t="inlineStr">
         <is>
           <t>APPROXIMATE (81%)</t>
         </is>
       </c>
-      <c r="G48" s="13" t="inlineStr">
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: A3.5)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
-Web search (not in Price Match) · APPROXIMATE (81%) · Matching: brand, form/spec, pack size · Not matching: product name · Variant mismatch: ordered A3.5, page sells A3. · VARIANT MISMATCH — shade mismatch (ordered A3.5, page A3); wrong variant, routed to alternate, VERIFY</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="n">
+Web search (not in Price Match) · APPROXIMATE (81%) · Matching: brand, form/spec, pack size · Not matching: product name · price $312.41 from page structured data (single offer) · Variant mismatch: ordered A3.5, page sells A3. · VARIANT MISMATCH — shade mismatch (ordered A3.5, page A3); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
         <v>60.25</v>
       </c>
     </row>
-    <row r="49" ht="64" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="57" ht="64" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>Fuji II LC Capsules A3.5 48/Bx
+SKU: 3333468  ·  Schein price: $372.66/unit</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>Fuji II LC Capsules A4 48/Bx</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>crazydentalprices.com</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>331.97</v>
+      </c>
+      <c r="E57" s="16" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Fuji-II-LC-Capsules-425005?leadsource=Jolt_CDP</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (81%)</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: A3.5)
+CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (81%) · Matching: brand, form/spec, pack size · Not matching: product name · Variant is A4, not A3.5. · VARIANT MISMATCH — shade mismatch (ordered A3.5, page A4); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>40.69</v>
+      </c>
+    </row>
+    <row r="58" ht="64" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>Fuji II LC Capsules A3 48/Bx
+SKU: 3333466  ·  Schein price: $372.66/unit</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>Fuji II LC Capsules A4 48/Bx</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>crazydentalprices.com</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>331.97</v>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Fuji-II-LC-Capsules-425005?leadsource=Jolt_CDP</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>APPROXIMATE (83%)</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: A3)
+CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
+Web search (not in Price Match) · APPROXIMATE (83%) · Matching: brand, form/spec, pack size · Not matching: product name · Variant (shade) mismatch: ordered A3, page is A4. · VARIANT MISMATCH — shade mismatch (ordered A3, page A4); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>40.69</v>
+      </c>
+    </row>
+    <row r="59" ht="64" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
 SKU: 3120212  ·  Schein price: $36.80/unit</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>Genie VPS Rapid Set Light Body 50mL 2/Pk</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D59" s="11" t="n">
         <v>39.99</v>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E59" s="12" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Genie-VPS-77610</t>
         </is>
       </c>
-      <c r="F49" s="10" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (83%)</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: XLight Body)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (83%) · Matching: brand, form/spec, pack size · Not matching: product name · The ordered variant is 'XLight Body', but the page sells 'Light Body'. This is a variant mismatch.</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>Equiv $39.99 &gt; Schein $36.80</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="64" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="60" ht="64" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
 SKU: 3120212  ·  Schein price: $36.80/unit</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Genie VPS Heavy Body Impression Material 2/Pack</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>practicon.com</t>
         </is>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D60" s="7" t="n">
         <v>44.99</v>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>https://www.practicon.com/genie-vps-heavy-body-impression-material-2-pack/p/7013484</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: XLight Body)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, form/spec, pack size · Not matching: product name · Product is 'Heavy Body' not 'XLight Body' as ordered. Pack quantity matches.</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>Equiv $44.99 &gt; Schein $36.80</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="64" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="61" ht="64" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Diamond FG Coarse 841G-012 5/Pk
 SKU: 7011085  ·  Schein price: $43.65/unit</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>Meisinger - Diamond Burs Round Edge Cylinder</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>dentalcity.com</t>
         </is>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D61" s="11" t="n">
         <v>49.99</v>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>https://www.dentalcity.com/product/22071/meisinger-diamond-burs-round-edge-cylinder?70-842012FG=</t>
         </is>
       </c>
-      <c r="F51" s="10" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>APPROXIMATE (79%)</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: 841G-012)
 CLOSE — same category, compatible specs, minor differences; substitution likely acceptable
 Web search (not in Price Match) · APPROXIMATE (79%) · Matching: brand, form/spec, pack size · Not matching: product name · The ordered variant is 'Diamond FG Coarse 841G-012'. The page lists 'Meisinger Diamond Round Edge Cylinder 1.2 mm Coarse FG 841G-012-FG 5/Pack'. The product name is 'Meisinger - Diamond Burs Round Edge Cylinder'. The ordered product is 'Diamond FG Coarse'. The page product is 'Meisinger Diamond Round Edge Cylinder'. The brand 'Meisinger' matches. The variant '841G-012' matches the '841G-012-FG' on the page. The pack quantity of 5 matches. However, the product name 'Diamond FG Coarse' is not an exact match for 'Meisinger Diamond Round Edge Cylinder', leading to name_match=false. The MPN '841G-012-FG' matches the ordered variant and MPN.</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>Equiv $49.99 &gt; Schein $43.65</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="64" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk
 SKU: 8889527  ·  Schein price: $71.70/unit</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Coltene ParaPost Fiber Lux/Taper Lux Posts</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>amtouch.com</t>
         </is>
       </c>
-      <c r="D52" s="7" t="n">
+      <c r="D62" s="7" t="n">
         <v>87.06999999999999</v>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>https://www.amtouch.com/shop-by-category/pins-posts/coltene-parapost-fiber-lux-taper-lux-posts/</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (65%)</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered 5) · VARIANT MISMATCH (ordered: Red)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (65%) · Matching: brand, product name, form/spec · Not matching: pack size · variant-matrix price $87.07 (page SKU WDT-PF1715 == order MPN PF1715) · Page lists a price range, but no specific variant or pack quantity is clearly priced for the ordered 'Red 5/Pk'. The displayed price is for an unspecified variant/pack.</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
+Web search (not in Price Match) · POSSIBLE (65%) · Matching: brand, product name, form/spec · Not matching: pack size · variant-matrix price $87.07 (ordered variant by SKU/MPN: WDT-PF1715) · Page lists a price range, but no specific variant or pack quantity is clearly priced for the ordered 'Red 5/Pk'. The displayed price is for an unspecified variant/pack.</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>Equiv $87.07 &gt; Schein $71.70</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="64" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
+    <row r="63" ht="64" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>Mity K-Files 25mm #10 6/Pk
 SKU: 2013820  ·  Schein price: $25.40/unit</t>
         </is>
       </c>
-      <c r="B53" s="13" t="inlineStr">
+      <c r="B63" s="13" t="inlineStr">
         <is>
           <t>25mm Size 10 H Files Hedstrom Endodontic Stainless Steel Dental Root Canal Files (Pack of 6)</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>myddssupply.com</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D63" s="15" t="n">
         <v>3.99</v>
       </c>
-      <c r="E53" s="16" t="inlineStr">
+      <c r="E63" s="16" t="inlineStr">
         <is>
           <t>https://myddssupply.com/products/25mm-size-10-h-files-endodontic-stainless-steel-dental-root-canal-files-pack-of-6</t>
         </is>
       </c>
-      <c r="F53" s="14" t="inlineStr">
+      <c r="F63" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (58%)</t>
         </is>
       </c>
-      <c r="G53" s="13" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: #10 25mm)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (58%) · Matching: form/spec, pack size · Not matching: brand, product name · Product is 'H Files Hedstrom' not 'Mity K-Files'. Brand is not Dentsply Sirona. Variant and pack quantity match the order. · PRICE UNRELIABLE — $3.99 is far below the other sources for this item (median $11.49); likely a related-item or single-unit price, VERIFY MANUALLY</t>
         </is>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H63" s="15" t="n">
         <v>21.41</v>
       </c>
     </row>
-    <row r="54" ht="64" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
+    <row r="64" ht="64" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>Mity K-Files 25mm #10 6/Pk
 SKU: 2013820  ·  Schein price: $25.40/unit</t>
         </is>
       </c>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="B64" s="13" t="inlineStr">
         <is>
           <t>K-files 25mm 6pk (Mani)</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>angeldentalsupply.com</t>
         </is>
       </c>
-      <c r="D54" s="15" t="n">
+      <c r="D64" s="15" t="n">
         <v>5.25</v>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>https://angeldentalsupply.com/product/k-files-25mm-6pk-mani/</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F64" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (58%)</t>
         </is>
       </c>
-      <c r="G54" s="13" t="inlineStr">
+      <c r="G64" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: #10 25mm)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (58%) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Mani vs Dentsply Sirona).</t>
         </is>
       </c>
-      <c r="H54" s="15" t="n">
+      <c r="H64" s="15" t="n">
         <v>20.15</v>
       </c>
     </row>
-    <row r="55" ht="64" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
+    <row r="65" ht="64" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>Mity K-Files 25mm #10 6/Pk
 SKU: 2013820  ·  Schein price: $25.40/unit</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B65" s="13" t="inlineStr">
         <is>
           <t>Kerr K-Files 25mm Size 35 Green 6/Pack</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>practicon.com</t>
         </is>
       </c>
-      <c r="D55" s="15" t="n">
+      <c r="D65" s="15" t="n">
         <v>10.99</v>
       </c>
-      <c r="E55" s="16" t="inlineStr">
+      <c r="E65" s="16" t="inlineStr">
         <is>
           <t>https://www.practicon.com/kerr-k-files-25mm-size-35-green-6-pack/p/71379163</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F65" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (60%)</t>
         </is>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: #10 25mm)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (60%) · Matching: form/spec, pack size · Not matching: brand, product name · Brand is Kerr, not Dentsply Sirona. Variant is Size 35 Green, not #10. · VARIANT MISMATCH — size mismatch (ordered #10, page #35); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H55" s="15" t="n">
+      <c r="H65" s="15" t="n">
         <v>14.41</v>
       </c>
     </row>
-    <row r="56" ht="64" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Mity K-Files 25mm #10 6/Pk
 SKU: 2013820  ·  Schein price: $25.40/unit</t>
         </is>
       </c>
-      <c r="B56" s="13" t="inlineStr">
+      <c r="B66" s="13" t="inlineStr">
         <is>
           <t>Kerr - K-Files 25mm</t>
         </is>
       </c>
-      <c r="C56" s="14" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>dentalcity.com</t>
         </is>
       </c>
-      <c r="D56" s="15" t="n">
+      <c r="D66" s="15" t="n">
         <v>18.79</v>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="E66" s="16" t="inlineStr">
         <is>
           <t>https://dentalcity.com/product/7571/kerr-k-files-25mm</t>
         </is>
       </c>
-      <c r="F56" s="14" t="inlineStr">
+      <c r="F66" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (58%)</t>
         </is>
       </c>
-      <c r="G56" s="13" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: #10 25mm)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (58%) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch (Kerr vs Dentsply Sirona) and product name mismatch (K-Files vs Mity K-Files). Variant color is also different (Purple vs not specified but implied standard).</t>
         </is>
       </c>
-      <c r="H56" s="15" t="n">
+      <c r="H66" s="15" t="n">
         <v>6.61</v>
       </c>
     </row>
-    <row r="57" ht="64" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+    <row r="67" ht="64" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
         <is>
           <t>Mity K-Files 25mm #10 6/Pk
 SKU: 2013820  ·  Schein price: $25.40/unit</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
+      <c r="B67" s="9" t="inlineStr">
         <is>
           <t>Kerr Endodontics K-Files 25mm #45-80 Assorted 6/Box.</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D67" s="11" t="n">
         <v>25.05</v>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E67" s="12" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/sybronendo-kfiles-25mm-4580-assorted-6-stainless-d-26612</t>
         </is>
       </c>
-      <c r="F57" s="10" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (54%)</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: #10 25mm)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (54%) · Matching: form/spec, pack size · Not matching: brand, product name · price set from net32.com seller table: lowest available (incl. shipping) of 5 seller(s), via Lowest Price row · Brand and product name mismatch. Ordered Dentsply Sirona Mity K-Files, page is Kerr Endodontics K-Files. Variant also does not match. · VARIANT MISMATCH — size mismatch (ordered #10, page #45); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H57" s="11" t="n">
+      <c r="H67" s="11" t="n">
         <v>0.35</v>
       </c>
     </row>
-    <row r="58" ht="64" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
+    <row r="68" ht="64" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="B68" s="13" t="inlineStr">
         <is>
           <t>Cranberry S3 Face Mask Blue Level 3 50/Bx</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D58" s="15" t="n">
+      <c r="D68" s="15" t="n">
         <v>7.93</v>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="E68" s="16" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/cranberry-s3-face-mask-blue-level-3-50-bx-pro2-solutions-s3160b</t>
         </is>
       </c>
-      <c r="F58" s="14" t="inlineStr">
+      <c r="F68" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (19%)</t>
         </is>
       </c>
-      <c r="G58" s="13" t="inlineStr">
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered 50) · VARIANT MISMATCH (ordered: L3 Black)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (19%) · Matching: form/spec · Not matching: brand, product name, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 4 seller(s), via min of Total column · Page is for Cranberry S3 Face Mask Blue, not Henry Schein S3+ Face Masks L3 Black. No pricing information available. · VARIANT MISMATCH — color mismatch (ordered black, page blue); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H58" s="15" t="n">
+      <c r="H68" s="15" t="n">
         <v>1.62</v>
       </c>
     </row>
-    <row r="59" ht="64" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
+    <row r="69" ht="64" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>50 4-Ply ASTM Level 3 Black w/ White Stripe Surgical Masks by PlastCare USA</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
         <is>
           <t>myddssupply.com</t>
         </is>
       </c>
-      <c r="D59" s="11" t="n">
+      <c r="D69" s="11" t="n">
         <v>11.99</v>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>https://myddssupply.com/products/4-ply-astm-level-3-black-w-white-stripe-surgical-masks-box-of-50-by-plastcare-usa</t>
         </is>
       </c>
-      <c r="F59" s="10" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (66%)</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: L3 Black)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (66%) · Matching: form/spec, pack size · Not matching: brand, product name · Brand and product name do not match. Page sells 'PlastCare USA' brand, buyer ordered 'Henry Schein S3+'. Page sells 'Black w/ White Stripe', buyer ordered 'L3 Black'.</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Equiv $11.99 &gt; Schein $9.55</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="64" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="70" ht="64" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>S3 Plus Mask Black 50/Box ASTM Level 3, S3160K</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>frontierdental.com</t>
         </is>
       </c>
-      <c r="D60" s="7" t="n">
+      <c r="D70" s="7" t="n">
         <v>13.05</v>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>https://frontierdental.com/us/en/product/s3-plus-mask-black-50box-astm-level-3-s3160k-165924?bp=ZnJvbnRpZXJkZW50YWw%3D&amp;ctr=VVM%3D</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (83%)</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (83%) · Matching: product name, form/spec, pack size · Not matching: brand · Brand mismatch: Ordered Henry Schein, page is Cranberry. Name mismatch: Ordered S3+ Face Masks, page is S3 Plus Mask.</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>Equiv $13.05 &gt; Schein $9.55</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="64" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
+    <row r="71" ht="64" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>Cranberry S3+ Procedure Face Mask ASTM Level 3 Black Box of 50</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>shop.benco.com</t>
         </is>
       </c>
-      <c r="D61" s="11" t="n">
+      <c r="D71" s="11" t="n">
         <v>17.99</v>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E71" s="12" t="inlineStr">
         <is>
           <t>https://shop.benco.com/Product/5747-640/cranberry-s3-procedure-face-mask-astm-level-3-blac</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F71" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (68%)</t>
         </is>
       </c>
-      <c r="G61" s="9" t="inlineStr">
+      <c r="G71" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: L3 Black)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (68%) · Matching: form/spec, pack size · Not matching: brand, product name · Brand mismatch: Ordered Henry Schein, page is Cranberry. Name mismatch: Ordered S3+ Face Masks, page is S3+ Procedure Face Mask.</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>Equiv $17.99 &gt; Schein $9.55</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="64" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="72" ht="64" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>1000 TULIP 4-Ply ASTM Level 3 Black Surgical Masks (20 Boxes of 50) *Bulk Special*</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>myddssupply.com</t>
         </is>
       </c>
-      <c r="D62" s="7" t="n">
+      <c r="D72" s="7" t="n">
         <v>139.99</v>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>https://myddssupply.com/products/1000-tulip-4-ply-astm-level-3-black-surgical-masks-20-boxes-of-50-bulk-special</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (47%)</t>
         </is>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 1000 vs ordered 50) · VARIANT MISMATCH (ordered: L3 Black)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (47%) · Matching: form/spec · Not matching: brand, product name, pack size · Brand is Tulip, not Henry Schein. Pack quantity is 1000 (20 boxes of 50), not 50. · PACK MISMATCH — page is 1000/pack but ordered 50/pack (20× off); different unit, routed to alternate</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H72" s="6" t="inlineStr">
         <is>
           <t>Equiv $139.99 &gt; Schein $9.55</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="64" customHeight="1">
-      <c r="A63" s="13" t="inlineStr">
+    <row r="73" ht="64" customHeight="1">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>Mixing Tips Reﬁll Teal 50mL 48/Bx
 SKU: 2223852  ·  Schein price: $70.13/unit</t>
         </is>
       </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>Pink Mixing Tips Medium (5.4 mm) (Bag of 48 Tips)</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="inlineStr">
-        <is>
-          <t>myddssupply.com</t>
-        </is>
-      </c>
-      <c r="D63" s="15" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>https://myddssupply.com/products/pink-mixing-tips-bag-of-48</t>
-        </is>
-      </c>
-      <c r="F63" s="14" t="inlineStr">
-        <is>
-          <t>POSSIBLE (47%)</t>
-        </is>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>Impression Mixing Tips Long Green/Teal (6.5mm) | 48/pkg</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>stardentalsupplies.com</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>https://stardentalsupplies.com/product/impression-mixing-tips-long-green-teal-48-pkg/</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (35%)</t>
+        </is>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
         <is>
           <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Teal)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (47%) · Matching: pack size · Not matching: brand, product name, form/spec · price $18.99 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Brand 'DMG' not found. Product name 'Pink Mixing Tips' does not match 'Mixing Tips'. Variant 'Pink' does not match 'Teal'. Size/form '5.4 mm' does not match '50mL'. · VARIANT MISMATCH — color mismatch (ordered teal, page pink); wrong variant, routed to alternate, VERIFY</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="n">
-        <v>51.14</v>
-      </c>
-    </row>
-    <row r="64" ht="64" customHeight="1">
-      <c r="A64" s="13" t="inlineStr">
+Web search (not in Price Match) · POSSIBLE (35%) · Matching: pack size · Not matching: brand, product name, form/spec · price $9.95 from page structured data (single offer) · Price not found for the main product. Prices shown are for unrelated products. · PRICE UNRELIABLE — $9.95 is far below the other sources for this item (median $30.00); likely a related-item or single-unit price, VERIFY MANUALLY</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>60.18</v>
+      </c>
+    </row>
+    <row r="74" ht="64" customHeight="1">
+      <c r="A74" s="13" t="inlineStr">
         <is>
           <t>Mixing Tips Reﬁll Teal 50mL 48/Bx
 SKU: 2223852  ·  Schein price: $70.13/unit</t>
         </is>
       </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>Yellow Mixing Tips Medium (4.2 mm) (Bag of 48 Tips)</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>myddssupply.com</t>
-        </is>
-      </c>
-      <c r="D64" s="15" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>https://myddssupply.com/products/yellow-mixing-tips-medium-4-2-mm-bag-of-48-tips</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
-        <is>
-          <t>POSSIBLE (47%)</t>
-        </is>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>Impression Mixing Tips (5.0mm) Short Green/Teal (For Heavy Body Materials) | 48/pkg</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>stardentalsupplies.com</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>https://stardentalsupplies.com/product/impression-mixing-tip-short-green-teal-for-heavy-body-materials-48-pkg/</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (35%)</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
         <is>
           <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Teal)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (47%) · Matching: pack size · Not matching: brand, product name, form/spec · Brand 'DMG' not found. Product name 'Yellow Mixing Tips' does not match 'Mixing Tips'. Variant 'Yellow' does not match 'Teal'. Size/form '4.2 mm' does not match '50mL'. · VARIANT MISMATCH — color mismatch (ordered teal, page yellow); wrong variant, routed to alternate, VERIFY</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="n">
-        <v>51.14</v>
-      </c>
-    </row>
-    <row r="65" ht="64" customHeight="1">
-      <c r="A65" s="13" t="inlineStr">
+Web search (not in Price Match) · POSSIBLE (35%) · Matching: pack size · Not matching: brand, product name, form/spec · price $12.95 from page structured data (single offer) · Price not found for the main product. Prices shown are for unrelated products. · PRICE UNRELIABLE — $12.95 is far below the other sources for this item (median $30.00); likely a related-item or single-unit price, VERIFY MANUALLY</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>57.18</v>
+      </c>
+    </row>
+    <row r="75" ht="64" customHeight="1">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>Mixing Tips Reﬁll Teal 50mL 48/Bx
 SKU: 2223852  ·  Schein price: $70.13/unit</t>
         </is>
       </c>
-      <c r="B65" s="13" t="inlineStr">
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>Parkell Mixing Tips with Aqua Base for MucoSoft, MucoHard , Sharp &amp; Cinch, pack</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>net32.com</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/parkell-mixing-tips-aqua-base-mucosoft-mucohard-d-151744</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (20%)</t>
+        </is>
+      </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page ? vs ordered 48) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Teal)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (20%) · Not matching: brand, product name, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 2 seller(s), via Lowest Price row · Product is 'Parkell Mixing Tips', not 'DMG Mixing Tips'. · VARIANT MISMATCH — color mismatch (ordered teal, page aqua); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>34.14</v>
+      </c>
+    </row>
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>Mixing Tips Reﬁll Teal 50mL 48/Bx
+SKU: 2223852  ·  Schein price: $70.13/unit</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
         <is>
           <t>Large Green Mixing Tips - 48/Bag</t>
         </is>
       </c>
-      <c r="C65" s="14" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
         <is>
           <t>pstshop.com</t>
         </is>
       </c>
-      <c r="D65" s="15" t="n">
+      <c r="D76" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E76" s="16" t="inlineStr">
         <is>
           <t>https://www.pstshop.com/large-green-mixing-tips-48-bag/</t>
         </is>
       </c>
-      <c r="F65" s="14" t="inlineStr">
+      <c r="F76" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (58%)</t>
         </is>
       </c>
-      <c r="G65" s="13" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Teal)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (58%) · Matching: form/spec, pack size · Not matching: brand, product name · price $48.00 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Brand and variant mismatch. Ordered DMG Teal, page is generic Green. · VARIANT MISMATCH — color mismatch (ordered teal, page green); wrong variant, routed to alternate, VERIFY</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="n">
+Web search (not in Price Match) · POSSIBLE (58%) · Matching: form/spec, pack size · Not matching: brand, product name · price $48.00 from page structured data (single offer) · Brand and variant mismatch. Ordered DMG Teal, page is generic Green. · VARIANT MISMATCH — color mismatch (ordered teal, page green); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="n">
         <v>22.13</v>
       </c>
     </row>
-    <row r="66" ht="64" customHeight="1">
-      <c r="A66" s="13" t="inlineStr">
+    <row r="77" ht="64" customHeight="1">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk
 SKU: 2222660  ·  Schein price: $76.60/unit</t>
         </is>
       </c>
-      <c r="B66" s="13" t="inlineStr">
+      <c r="B77" s="13" t="inlineStr">
         <is>
           <t>Yellow Mixing Tips Medium (4.2 mm) (Bag of 48 Tips)</t>
         </is>
       </c>
-      <c r="C66" s="14" t="inlineStr">
+      <c r="C77" s="14" t="inlineStr">
         <is>
           <t>myddssupply.com</t>
         </is>
       </c>
-      <c r="D66" s="15" t="n">
+      <c r="D77" s="15" t="n">
         <v>18.99</v>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E77" s="16" t="inlineStr">
         <is>
           <t>https://myddssupply.com/products/yellow-mixing-tips-medium-4-2-mm-bag-of-48-tips</t>
         </is>
       </c>
-      <c r="F66" s="14" t="inlineStr">
+      <c r="F77" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (35%)</t>
         </is>
       </c>
-      <c r="G66" s="13" t="inlineStr">
+      <c r="G77" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 48 vs ordered 40) · VARIANT MISMATCH (ordered: Yellow w/LuerLock)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (35%) · Matching: form/spec · Not matching: brand, product name, pack size · price $18.99 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Product is Kulzer Dynamic Mixing Tips Yellow w/LuerLock 40/Pk. Page shows generic Yellow Mixing Tips, 48 tips, and no LuerLock. It is backordered. · PRICE UNRELIABLE — $18.99 is far below the other sources for this item (median $60.91); likely a related-item or single-unit price, VERIFY MANUALLY</t>
         </is>
       </c>
-      <c r="H66" s="15" t="n">
+      <c r="H77" s="15" t="n">
         <v>57.61</v>
       </c>
     </row>
-    <row r="67" ht="64" customHeight="1">
-      <c r="A67" s="13" t="inlineStr">
+    <row r="78" ht="64" customHeight="1">
+      <c r="A78" s="13" t="inlineStr">
         <is>
           <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk
 SKU: 2222660  ·  Schein price: $76.60/unit</t>
         </is>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B78" s="13" t="inlineStr">
         <is>
           <t>Dynamic Mixing Tips | Yellow, 50/Pkg., 34746</t>
         </is>
       </c>
-      <c r="C67" s="14" t="inlineStr">
+      <c r="C78" s="14" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D67" s="15" t="n">
+      <c r="D78" s="15" t="n">
         <v>60.91</v>
       </c>
-      <c r="E67" s="16" t="inlineStr">
+      <c r="E78" s="16" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/dynamic-mixing-tips-yellow-50-pkg-34746-kerr-34746</t>
         </is>
       </c>
-      <c r="F67" s="14" t="inlineStr">
+      <c r="F78" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (35%)</t>
         </is>
       </c>
-      <c r="G67" s="13" t="inlineStr">
+      <c r="G78" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 50 vs ordered 40) · VARIANT MISMATCH (ordered: Yellow w/LuerLock)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (35%) · Matching: form/spec · Not matching: brand, product name, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 5 seller(s), via min of Total column · Page is an aggregator but no prices are visible. Product is Kulzer Dynamic Mixing Tips Yellow w/LuerLock 40/Pk. Page shows 50/Pkg and no LuerLock.</t>
         </is>
       </c>
-      <c r="H67" s="15" t="n">
+      <c r="H78" s="15" t="n">
         <v>15.69</v>
       </c>
     </row>
-    <row r="68" ht="64" customHeight="1">
-      <c r="A68" s="13" t="inlineStr">
+    <row r="79" ht="64" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
         <is>
           <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk
 SKU: 2222660  ·  Schein price: $76.60/unit</t>
         </is>
       </c>
-      <c r="B68" s="13" t="inlineStr">
+      <c r="B79" s="13" t="inlineStr">
         <is>
           <t>Dynamic Mixing Tips 380 mL Yellow (50 tip +2 rings) Kerr</t>
         </is>
       </c>
-      <c r="C68" s="14" t="inlineStr">
+      <c r="C79" s="14" t="inlineStr">
         <is>
           <t>skydentalsupply.com</t>
         </is>
       </c>
-      <c r="D68" s="15" t="n">
+      <c r="D79" s="15" t="n">
         <v>65.98999999999999</v>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E79" s="16" t="inlineStr">
         <is>
           <t>https://www.skydentalsupply.com/dynamic-mixingtips-34746.htm</t>
         </is>
       </c>
-      <c r="F68" s="14" t="inlineStr">
+      <c r="F79" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (43%)</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="G79" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 50 vs ordered 40) · VARIANT MISMATCH (ordered: Yellow w/LuerLock)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (43%) · Matching: form/spec · Not matching: brand, product name, pack size · Brand mismatch (Kulzer vs Kerr). Pack quantity mismatch (40 vs 50). Variant mismatch (Yellow w/LuerLock vs Yellow (50 tip +2 rings)). MPN mismatch (CW-6162 vs 34746).</t>
         </is>
       </c>
-      <c r="H68" s="15" t="n">
+      <c r="H79" s="15" t="n">
         <v>10.61</v>
       </c>
     </row>
-    <row r="69" ht="64" customHeight="1">
-      <c r="A69" s="13" t="inlineStr">
+    <row r="80" ht="64" customHeight="1">
+      <c r="A80" s="13" t="inlineStr">
         <is>
           <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk
 SKU: 2222660  ·  Schein price: $76.60/unit</t>
         </is>
       </c>
-      <c r="B69" s="13" t="inlineStr">
+      <c r="B80" s="13" t="inlineStr">
         <is>
           <t>Dynamic Yellow Mixing Tips 50/Pk</t>
         </is>
       </c>
-      <c r="C69" s="14" t="inlineStr">
+      <c r="C80" s="14" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D69" s="15" t="n">
+      <c r="D80" s="15" t="n">
         <v>66.48999999999999</v>
       </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="E80" s="16" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Kerr-34746?leadsource=Jolt_CDP</t>
         </is>
       </c>
-      <c r="F69" s="14" t="inlineStr">
+      <c r="F80" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (43%)</t>
         </is>
       </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="G80" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 50 vs ordered 40) · VARIANT MISMATCH (ordered: Yellow w/LuerLock)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (43%) · Matching: form/spec · Not matching: brand, product name, pack size · Brand mismatch (Kulzer vs Kerr). Pack quantity mismatch (40 vs 50). Variant mismatch (Yellow w/LuerLock vs Yellow). MPN mismatch (CW-6162 vs 813-34746).</t>
         </is>
       </c>
-      <c r="H69" s="15" t="n">
+      <c r="H80" s="15" t="n">
         <v>10.11</v>
       </c>
     </row>
-    <row r="70" ht="64" customHeight="1">
-      <c r="A70" s="13" t="inlineStr">
+    <row r="81" ht="64" customHeight="1">
+      <c r="A81" s="13" t="inlineStr">
         <is>
           <t>Genie VPS Magic Mix Stand Bulk Heavy Body 4/Pk
 SKU: 3120199  ·  Schein price: $518.89/unit</t>
         </is>
       </c>
-      <c r="B70" s="13" t="inlineStr">
+      <c r="B81" s="13" t="inlineStr">
         <is>
           <t>Genie Magic Mix</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
+      <c r="C81" s="14" t="inlineStr">
         <is>
           <t>safcodental.com</t>
         </is>
       </c>
-      <c r="D70" s="15" t="n">
+      <c r="D81" s="15" t="n">
         <v>73.98999999999999</v>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E81" s="16" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/product/genie-reg-magic-mix</t>
         </is>
       </c>
-      <c r="F70" s="14" t="inlineStr">
+      <c r="F81" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (39%)</t>
         </is>
       </c>
-      <c r="G70" s="13" t="inlineStr">
+      <c r="G81" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered 4) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (39%) · Matching: brand · Not matching: product name, form/spec, pack size · The page lists 'Genie Magic Mix' starting 'From $73.99' but does not specify the 'Stand Bulk Heavy Body' variant or a 4-pack. The price is a 'from' price, and no specific pack quantity or variant is available to price. · PRICE UNRELIABLE — $73.99 is far below the other sources for this item (median $360.10); likely a related-item or single-unit price, VERIFY MANUALLY</t>
-        </is>
-      </c>
-      <c r="H70" s="15" t="n">
+Web search (not in Price Match) · POSSIBLE (39%) · Matching: brand · Not matching: product name, form/spec, pack size · The page lists 'Genie Magic Mix' starting 'From $73.99' but does not specify the 'Stand Bulk Heavy Body' variant or a 4-pack. The price is a 'from' price, and no specific pack quantity or variant is available to price. · PRICE UNRELIABLE — $73.99 is far below the other sources for this item (median $495.95); likely a related-item or single-unit price, VERIFY MANUALLY</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="n">
         <v>444.9</v>
       </c>
     </row>
-    <row r="71" ht="64" customHeight="1">
-      <c r="A71" s="13" t="inlineStr">
+    <row r="82" ht="64" customHeight="1">
+      <c r="A82" s="13" t="inlineStr">
         <is>
           <t>Genie VPS Magic Mix Stand Bulk Heavy Body 4/Pk
 SKU: 3120199  ·  Schein price: $518.89/unit</t>
         </is>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B82" s="13" t="inlineStr">
         <is>
           <t>Genie Magic Mix VPS Heavy Body Standard Set Berry Flavor, Purple, 380 mL Redesigned Cartridge</t>
         </is>
       </c>
-      <c r="C71" s="14" t="inlineStr">
+      <c r="C82" s="14" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D71" s="15" t="n">
+      <c r="D82" s="15" t="n">
         <v>174.31</v>
       </c>
-      <c r="E71" s="16" t="inlineStr">
+      <c r="E82" s="16" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/genie-magic-mix-vps-impression-material-heavy-d-172996</t>
         </is>
       </c>
-      <c r="F71" s="14" t="inlineStr">
+      <c r="F82" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (50%)</t>
         </is>
       </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="G82" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered 4)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (50%) · Matching: product name, form/spec · Not matching: brand, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 2 seller(s), via Lowest Price row · Brand mismatch (Sultan vs Henry Schein). Product name mismatch (Standard Set Berry Flavor, Purple vs Stand Bulk). Pack quantity not specified on page. · PRICE SUSPECT — locked $174.31 is far below the other sellers for this item (median $500.43); the seller-table parse may have caught a stray number, VERIFY</t>
         </is>
       </c>
-      <c r="H71" s="15" t="n">
+      <c r="H82" s="15" t="n">
         <v>344.58</v>
       </c>
     </row>
-    <row r="72" ht="64" customHeight="1">
-      <c r="A72" s="13" t="inlineStr">
+    <row r="83" ht="64" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>Speedclean For Autoclave 16oz/Bt
 SKU: 3865728  ·  Schein price: $35.99/unit</t>
         </is>
       </c>
-      <c r="B72" s="13" t="inlineStr">
+      <c r="B83" s="13" t="inlineStr">
         <is>
           <t>Speed-clean Autoclave Cleaner Liquid 16oz/Bt</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
+      <c r="C83" s="14" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D72" s="15" t="n">
+      <c r="D83" s="15" t="n">
         <v>22.6</v>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="E83" s="16" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/speed-clean-autoclave-cleaner-liquid-16oz-bt-midmark-002-0396-00?kw=&amp;cpn=23795785166</t>
         </is>
       </c>
-      <c r="F72" s="14" t="inlineStr">
+      <c r="F83" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (4%)</t>
         </is>
       </c>
-      <c r="G72" s="13" t="inlineStr">
+      <c r="G83" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (4%) · Not matching: brand, product name, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 2 seller(s), via min of Total column · No pricing information found on the page. The product is 'Speed-clean' by Midmark, not 'Speedclean For Autoclave' by SciCan.</t>
         </is>
       </c>
-      <c r="H72" s="15" t="n">
+      <c r="H83" s="15" t="n">
         <v>13.39</v>
       </c>
     </row>
-    <row r="73" ht="64" customHeight="1">
-      <c r="A73" s="13" t="inlineStr">
+    <row r="84" ht="64" customHeight="1">
+      <c r="A84" s="13" t="inlineStr">
         <is>
           <t>Speedclean For Autoclave 16oz/Bt
 SKU: 3865728  ·  Schein price: $35.99/unit</t>
         </is>
       </c>
-      <c r="B73" s="13" t="inlineStr">
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>Speed-clean Autoclave Cleaner Liquid 16oz/Bt</t>
         </is>
       </c>
-      <c r="C73" s="14" t="inlineStr">
+      <c r="C84" s="14" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D73" s="15" t="n">
+      <c r="D84" s="15" t="n">
         <v>22.6</v>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/speed-clean-autoclave-cleaner-liquid-16oz-bt-midmark-002-0396-00</t>
         </is>
       </c>
-      <c r="F73" s="14" t="inlineStr">
+      <c r="F84" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (4%)</t>
         </is>
       </c>
-      <c r="G73" s="13" t="inlineStr">
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (4%) · Not matching: brand, product name, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 2 seller(s), via min of Total column · No pricing information found on the page. The product is 'Speed-clean' by Midmark, not 'Speedclean For Autoclave' by SciCan.</t>
         </is>
       </c>
-      <c r="H73" s="15" t="n">
+      <c r="H84" s="15" t="n">
         <v>13.39</v>
       </c>
     </row>
-    <row r="74" ht="64" customHeight="1">
-      <c r="A74" s="13" t="inlineStr">
+    <row r="85" ht="64" customHeight="1">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>Speedclean For Autoclave 16oz/Bt
 SKU: 3865728  ·  Schein price: $35.99/unit</t>
         </is>
       </c>
-      <c r="B74" s="13" t="inlineStr">
+      <c r="B85" s="13" t="inlineStr">
         <is>
           <t>SpeedClean Autoclave Cleaner - Breaks Down Chamber Deposits, for All Types</t>
         </is>
       </c>
-      <c r="C74" s="14" t="inlineStr">
+      <c r="C85" s="14" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D74" s="15" t="n">
+      <c r="D85" s="15" t="n">
         <v>26.94</v>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="E85" s="16" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/speedclean-autoclave-cleaner-breaks-chamber-deposits-types-d-29186</t>
         </is>
       </c>
-      <c r="F74" s="14" t="inlineStr">
+      <c r="F85" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (35%)</t>
         </is>
       </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="G85" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (35%) · Matching: product name · Not matching: brand, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 3 seller(s), via Lowest Price row · Brand mismatch (Midmark vs SciCan). No price found on page.</t>
         </is>
       </c>
-      <c r="H74" s="15" t="n">
+      <c r="H85" s="15" t="n">
         <v>9.050000000000001</v>
       </c>
     </row>
-    <row r="75" ht="64" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
+    <row r="86" ht="64" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Speedclean For Autoclave 16oz/Bt
 SKU: 3865728  ·  Schein price: $35.99/unit</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>SPEEDCLEAN - 16 OZ BOTTLE - QTY 1</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>shop.midmark.com</t>
         </is>
       </c>
-      <c r="D75" s="11" t="n">
+      <c r="D86" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>https://shop.midmark.com/product/002039600-speedclean-16-oz-bottle-qty-1/01t6g000005du3PAAQ</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (77%)</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (77%) · Matching: product name, form/spec, pack size · Not matching: brand · MPN mismatch. Ordered 002039605, page is 002-0396-00.</t>
         </is>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="H86" s="6" t="inlineStr">
         <is>
           <t>Equiv $56.00 &gt; Schein $35.99</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="64" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="87" ht="64" customHeight="1">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>Speedclean For Autoclave 16oz/Bt
 SKU: 3865728  ·  Schein price: $35.99/unit</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>SPEEDCLEAN - CASE OF QTY 12 - 16 OZ BOTTLES</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
         <is>
           <t>shop.midmark.com</t>
         </is>
       </c>
-      <c r="D76" s="7" t="n">
+      <c r="D87" s="11" t="n">
         <v>277</v>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>https://shop.midmark.com/product/002039605-speedclean-case-of-qty-12-16-oz-bottles/01t6g000005eBztAAE</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (64%)</t>
         </is>
       </c>
-      <c r="G76" s="5" t="inlineStr">
+      <c r="G87" s="9" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 12 vs ordered ?)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (64%) · Matching: product name, form/spec · Not matching: brand, pack size · MPN matches, but pack quantity is 12, not 1. Brand mismatch.</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="H87" s="10" t="inlineStr">
         <is>
           <t>Equiv $277.00 &gt; Schein $35.99</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="64" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
+    <row r="88" ht="64" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9736H-150 2/Pk
 SKU: 7013176  ·  Schein price: $66.58/unit</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>Meisinger - Ceramic Polishers</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>dentalcity.com</t>
         </is>
       </c>
-      <c r="D77" s="11" t="n">
+      <c r="D88" s="7" t="n">
         <v>67.69</v>
       </c>
-      <c r="E77" s="12" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>https://www.dentalcity.com/product/21767/meisinger-ceramic-polishers</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (43%)</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 1 vs ordered 2) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: specified)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (43%) · Matching: brand · Not matching: product name, form/spec, pack size · Product name, variant, and MPN do not match the ordered item. The page lists many variants, but the main product priced is different from the ordered one. Ordered MPN: 9736H-150-HP-TRQ, Page MPN: 9770G-260-HP-GR/O.</t>
         </is>
       </c>
-      <c r="H77" s="10" t="inlineStr">
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>Equiv $67.69 &gt; Schein $66.58</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="64" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="89" ht="64" customHeight="1">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
 SKU: 7120116  ·  Schein price: $13.35/unit</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B89" s="9" t="inlineStr">
         <is>
           <t>Toothbrush Gum Care Compact Adult Extra Soft 12/Pkg (Oral-B)</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C89" s="10" t="inlineStr">
         <is>
           <t>skydentalsupply.com</t>
         </is>
       </c>
-      <c r="D78" s="7" t="n">
+      <c r="D89" s="11" t="n">
         <v>15.29</v>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E89" s="12" t="inlineStr">
         <is>
           <t>https://www.skydentalsupply.com/oral-b-gum-care-compacttoothbrush-12.htm</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (64%)</t>
         </is>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G89" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Soft Compact)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (64%) · Matching: form/spec, pack size · Not matching: brand, product name · Brand is Oral-B, not Sunstar. Product name is 'Gum Care Compact' not 'Gum Technique Deep Clean'. Variant is 'Extra Soft' not 'Soft Compact'. Pack quantity matches. Product is out of stock.</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H89" s="10" t="inlineStr">
         <is>
           <t>Equiv $15.29 &gt; Schein $13.35</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="64" customHeight="1">
-      <c r="A79" s="9" t="inlineStr">
+    <row r="90" ht="64" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
 SKU: 7120116  ·  Schein price: $13.35/unit</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>Oral-B Gum Care Compact Adult Toothbrushes 12/Box</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>practicon.com</t>
         </is>
       </c>
-      <c r="D79" s="11" t="n">
+      <c r="D90" s="7" t="n">
         <v>22.49</v>
       </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>https://www.practicon.com/oral-b-gum-care-compact-adult-toothbrushes-12-box/p/71016284</t>
         </is>
       </c>
-      <c r="F79" s="10" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (43%)</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Soft Compact)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (43%) · Matching: pack size · Not matching: brand, product name, form/spec · Brand and product name do not match. Ordered Sunstar Gum Technique Deep Clean, page is Oral-B Gum Care Compact.</t>
         </is>
       </c>
-      <c r="H79" s="10" t="inlineStr">
+      <c r="H90" s="6" t="inlineStr">
         <is>
           <t>Equiv $22.49 &gt; Schein $13.35</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="64" customHeight="1">
-      <c r="A80" s="13" t="inlineStr">
+    <row r="91" ht="64" customHeight="1">
+      <c r="A91" s="13" t="inlineStr">
         <is>
           <t>Premium Cotton Rolls #2 Non-Sterile 2000/Bx
 SKU: 8969286  ·  Schein price: $33.80/unit</t>
         </is>
       </c>
-      <c r="B80" s="13" t="inlineStr">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>Safco Cotton Rolls - 2000/bx</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
+      <c r="C91" s="14" t="inlineStr">
         <is>
           <t>quantumlabs.com</t>
         </is>
       </c>
-      <c r="D80" s="15" t="n">
+      <c r="D91" s="15" t="n">
         <v>25.5</v>
       </c>
-      <c r="E80" s="16" t="inlineStr">
+      <c r="E91" s="16" t="inlineStr">
         <is>
           <t>https://quantumlabs.com/safco-cotton-rolls-med-2-2000bx</t>
         </is>
       </c>
-      <c r="F80" s="14" t="inlineStr">
+      <c r="F91" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (62%)</t>
         </is>
       </c>
-      <c r="G80" s="13" t="inlineStr">
+      <c r="G91" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: #2 Non-Sterile)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (62%) · Matching: form/spec, pack size · Not matching: brand, product name · Brand is Safco, not Henry Schein. Product name is 'Safco Cotton Rolls', not 'Premium Cotton Rolls'. MPN 1022470 does not match 8969286.</t>
         </is>
       </c>
-      <c r="H80" s="15" t="n">
+      <c r="H91" s="15" t="n">
         <v>8.300000000000001</v>
       </c>
     </row>
-    <row r="81" ht="64" customHeight="1">
-      <c r="A81" s="13" t="inlineStr">
+    <row r="92" ht="64" customHeight="1">
+      <c r="A92" s="13" t="inlineStr">
         <is>
           <t>Premium Cotton Rolls #2 Non-Sterile 2000/Bx
 SKU: 8969286  ·  Schein price: $33.80/unit</t>
         </is>
       </c>
-      <c r="B81" s="13" t="inlineStr">
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>Essentials Cotton Rolls, #2, Medium, 2000/Pk</t>
         </is>
       </c>
-      <c r="C81" s="14" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D81" s="15" t="n">
+      <c r="D92" s="15" t="n">
         <v>25.51</v>
       </c>
-      <c r="E81" s="16" t="inlineStr">
+      <c r="E92" s="16" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/essentials-cotton-rolls-2-medium-2000-pk-d-188840</t>
         </is>
       </c>
-      <c r="F81" s="14" t="inlineStr">
+      <c r="F92" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (20%)</t>
         </is>
       </c>
-      <c r="G81" s="13" t="inlineStr">
+      <c r="G92" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered 2000) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: #2 Non-Sterile)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (20%) · Not matching: brand, product name, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 1 seller(s), via Lowest Price row · Price not found on page. Product is 'Essentials Cotton Rolls' by '3D Dental', not 'Henry Schein Premium Cotton Rolls'.</t>
         </is>
       </c>
-      <c r="H81" s="15" t="n">
+      <c r="H92" s="15" t="n">
         <v>8.289999999999999</v>
       </c>
     </row>
-    <row r="82" ht="64" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="93" ht="64" customHeight="1">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>Premium Cotton Rolls #2 Non-Sterile 2000/Bx
 SKU: 8969286  ·  Schein price: $33.80/unit</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>Cotton Rolls #2 1.5" x 3/8 Medium N/S 2000/Bx</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D82" s="7" t="n">
+      <c r="D93" s="11" t="n">
         <v>34.99</v>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E93" s="12" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Cotton-Rolls-Crosstex-DNC</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (64%)</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G93" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: #2 Non-Sterile)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (64%) · Matching: form/spec, pack size · Not matching: brand, product name · Brand is Crosstex, not Henry Schein. Product name is 'Cotton Rolls', not 'Premium Cotton Rolls'. MPN 141-DNC does not match 8969286.</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="H93" s="10" t="inlineStr">
         <is>
           <t>Equiv $34.99 &gt; Schein $33.80</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="64" customHeight="1">
-      <c r="A83" s="13" t="inlineStr">
+    <row r="94" ht="64" customHeight="1">
+      <c r="A94" s="13" t="inlineStr">
         <is>
           <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk
 SKU: 7772551  ·  Schein price: $278.99/unit</t>
         </is>
       </c>
-      <c r="B83" s="13" t="inlineStr">
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>Clinpro Clear 2.1% Sodium Fluoride Treatment, 0.5 mL Unit Dose, Mint Flavor, 50/Pk</t>
         </is>
       </c>
-      <c r="C83" s="14" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D83" s="15" t="n">
+      <c r="D94" s="15" t="n">
         <v>120.44</v>
       </c>
-      <c r="E83" s="16" t="inlineStr">
+      <c r="E94" s="16" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/clinpro-clear-21-sodium-fluoride-treatment-05-d-182705</t>
         </is>
       </c>
-      <c r="F83" s="14" t="inlineStr">
+      <c r="F94" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (54%)</t>
         </is>
       </c>
-      <c r="G83" s="13" t="inlineStr">
+      <c r="G94" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 50 vs ordered 100) · VARIANT MISMATCH (ordered: No Flavor)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (54%) · Matching: brand, form/spec · Not matching: product name, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 8 seller(s), via Lowest Price row · Product is 'Mint Flavor' and '50/Pk', not 'No Flavor' and '100/Pk'. No price found. · VARIANT MISMATCH — flavor mismatch (ordered 'no flavor', page 'mint'); wrong variant, routed to alternate, VERIFY · PRICE SUSPECT — locked $120.44 is far below the other sellers for this item (median $241.00); the seller-table parse may have caught a stray number, VERIFY</t>
         </is>
       </c>
-      <c r="H83" s="15" t="n">
+      <c r="H94" s="15" t="n">
         <v>158.55</v>
       </c>
     </row>
-    <row r="84" ht="64" customHeight="1">
-      <c r="A84" s="13" t="inlineStr">
+    <row r="95" ht="64" customHeight="1">
+      <c r="A95" s="13" t="inlineStr">
         <is>
           <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
 SKU: 1024081  ·  Schein price: $28.89/unit</t>
         </is>
       </c>
-      <c r="B84" s="13" t="inlineStr">
+      <c r="B95" s="13" t="inlineStr">
         <is>
           <t>Top Quality Manufacturing Paper Tray Covers (Ritter), 8.5" x 12.25", Blue, 1000/Case</t>
         </is>
       </c>
-      <c r="C84" s="14" t="inlineStr">
+      <c r="C95" s="14" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D84" s="15" t="n">
+      <c r="D95" s="15" t="n">
         <v>24.75</v>
       </c>
-      <c r="E84" s="16" t="inlineStr">
+      <c r="E95" s="16" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/top-quality-manufacturing-paper-tray-covers-ritter-d-184701</t>
         </is>
       </c>
-      <c r="F84" s="14" t="inlineStr">
+      <c r="F95" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (69%)</t>
         </is>
       </c>
-      <c r="G84" s="13" t="inlineStr">
+      <c r="G95" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Aqua)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (69%) · Matching: brand, form/spec, pack size · Not matching: product name · price set from net32.com seller table: lowest available (incl. shipping) of 1 seller(s), via Lowest Price row · Price not found on page. Variant color mismatch (Blue vs Aqua). · VARIANT MISMATCH — color mismatch (ordered aqua, page blue); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H84" s="15" t="n">
+      <c r="H95" s="15" t="n">
         <v>4.14</v>
       </c>
     </row>
-    <row r="85" ht="64" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
+    <row r="96" ht="64" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
 SKU: 1024081  ·  Schein price: $28.89/unit</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>Essentials 8.5"x12.25" Ritter "B" Paper Tray Covers, Green, 1000/Pk</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D85" s="11" t="n">
+      <c r="D96" s="7" t="n">
         <v>31.95</v>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/essentials-85x1225-ritter-b-paper-tray-covers-d-188693</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (69%)</t>
         </is>
       </c>
-      <c r="G85" s="9" t="inlineStr">
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Aqua)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (69%) · Matching: brand, form/spec, pack size · Not matching: product name · price set from net32.com seller table: lowest available (incl. shipping) of 1 seller(s), via Lowest Price row · Price not found on page. Variant color mismatch (Green vs Aqua). · VARIANT MISMATCH — color mismatch (ordered aqua, page green); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H85" s="10" t="inlineStr">
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>Equiv $31.95 &gt; Schein $28.89</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="64" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="97" ht="64" customHeight="1">
+      <c r="A97" s="13" t="inlineStr">
         <is>
           <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx
 SKU: 1126830  ·  Schein price: $16.15/unit</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
-        <is>
-          <t>3000 PlastCare USA SMALL Cobalt-300 3.5 mil Indigo Blue Nitrile Exam Gloves (Powder &amp; Latex Free)</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>myddssupply.com</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="n">
-        <v>134.99</v>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>https://myddssupply.com/products/3000-plastcare-usa-small-cobalt-300-indigo-blue-nitrile-exam-gloves-powder-latex-free</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>Aurelia Sonic Nitrile Exam Gloves: Small 300/Bx</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>net32.com</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="E97" s="16" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/aurelia-sonic-nitrile-exam-gloves-small-300-d-151428</t>
+        </is>
+      </c>
+      <c r="F97" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (54%)</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G97" s="13" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Ice Blue Small)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (54%) · Matching: form/spec, pack size · Not matching: brand, product name · price $134.99 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Brand and product name do not match. Ordered Criterion N300, page is PlastCare USA Cobalt-300. Color is also different (Ice Blue vs Indigo Blue). · VARIANT MISMATCH — house-brand mismatch (ordered Criterion, page is a different brand); wrong variant, routed to alternate, VERIFY</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>Equiv $134.99 &gt; Schein $16.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="64" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
+Web search (not in Price Match) · POSSIBLE (54%) · Matching: form/spec, pack size · Not matching: brand, product name · price set from net32.com seller table: lowest available (incl. shipping) of 7 seller(s), via Lowest Price row · Brand and product name do not match. Ordered Criterion N300, page is Aurelia Sonic. · VARIANT MISMATCH — house-brand mismatch (ordered Criterion, page is a different brand); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="98" ht="64" customHeight="1">
+      <c r="A98" s="17" t="inlineStr">
         <is>
           <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx
 SKU: 1126830  ·  Schein price: $16.15/unit</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>18000 Small Aurelia Sonic-300 Blue Nitrile 2.2 mil Powder Free Examination Gloves (60 Boxes) *Bulk Special*</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>myddssupply.com</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="n">
-        <v>954.99</v>
-      </c>
-      <c r="E87" s="12" t="inlineStr">
-        <is>
-          <t>https://myddssupply.com/products/18000-small-aurelia-sonic-300-blue-nitrile-2-2-mil-powder-free-examination-gloves-60-boxes-bulk-special</t>
-        </is>
-      </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>Smile Blue Gloves (Nitrile) 300 Count</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>topqualitygloves.com</t>
+        </is>
+      </c>
+      <c r="D98" s="19" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>https://topqualitygloves.com/products/smile-blue-gloves-nitrile</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
         <is>
           <t>POSSIBLE (50%)</t>
         </is>
       </c>
-      <c r="G87" s="9" t="inlineStr">
+      <c r="G98" s="17" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Ice Blue Small)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (50%) · Matching: form/spec, pack size · Not matching: brand, product name · price $954.99 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Price not found on page. Brand and product name do not match. Ordered Criterion N300, page is Aurelia Sonic-300. Color is also different (Ice Blue vs Blue). · VARIANT MISMATCH — house-brand mismatch (ordered Criterion, page is a different brand); wrong variant, routed to alternate, VERIFY</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>Equiv $954.99 &gt; Schein $16.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="64" customHeight="1">
-      <c r="A88" s="13" t="inlineStr">
+Web search (not in Price Match) · POSSIBLE (50%) · Matching: form/spec, pack size · Not matching: brand, product name · price $14.99 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Product not available. Brand and name mismatch. · VARIANT MISMATCH — house-brand mismatch (ordered Criterion, page is a different brand); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H98" s="19" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="99" ht="64" customHeight="1">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx
+SKU: 1126830  ·  Schein price: $16.15/unit</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t>Dental City - Helium Powder Free Blue Nitrile Dental Gloves 300/Box</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>dentalcity.com</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>https://www.dentalcity.com/product/14422/dental-city-helium-powder-free-blue-nitrile-dental-gloves-300box</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>POSSIBLE (50%)</t>
+        </is>
+      </c>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Ice Blue Small)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (50%) · Matching: form/spec, pack size · Not matching: brand, product name · price $16.90 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Brand and product name do not match. The ordered product is 'Criterion N300 Nitrile Glove' while the page sells 'Dental City - Helium Powder Free Blue Nitrile Dental Gloves'. · VARIANT MISMATCH — house-brand mismatch (ordered Criterion, page is a different brand); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>Equiv $16.90 &gt; Schein $16.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="64" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx
+SKU: 1126830  ·  Schein price: $16.15/unit</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Henry Schein Gloves Exam Criterion N300 Ultra PF Nitrile LF XS Ice Blu</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>graylinemedical.com</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>https://www.graylinemedical.com/products/henry-schein-gloves-exam-criterion-n300-ultra-pf-nitrile-lf-xs-ice-blue-300-bx-10-bx-ca1126829</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>POSSIBLE (77%)</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (77%) · Matching: brand, product name, pack size · Not matching: form/spec · structured data: OUT OF STOCK · price $25.99 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Page sells 'XS' size, not 'Small'. No price found.</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>Equiv $25.99 &gt; Schein $16.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="64" customHeight="1">
+      <c r="A101" s="13" t="inlineStr">
         <is>
           <t>Criterion N300 Glove Ice Blue Nitrile M 300/Bx
 SKU: 1126831  ·  Schein price: $16.15/unit</t>
         </is>
       </c>
-      <c r="B88" s="13" t="inlineStr">
+      <c r="B101" s="13" t="inlineStr">
         <is>
           <t>Criterion N300 Nitrile Exam Gloves Medium Standard Ice Blue Non-Sterile, 10 BX/C</t>
         </is>
       </c>
-      <c r="C88" s="14" t="inlineStr">
+      <c r="C101" s="14" t="inlineStr">
         <is>
           <t>mfidistribution.com</t>
         </is>
       </c>
-      <c r="D88" s="15" t="n">
+      <c r="D101" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="E88" s="16" t="inlineStr">
+      <c r="E101" s="16" t="inlineStr">
         <is>
           <t>https://www.mfidistribution.com/product-page/criterion-n300-nitrile-exam-gloves-medium-standard-ice-blue-non-sterile-10-bx-c</t>
         </is>
       </c>
-      <c r="F88" s="14" t="inlineStr">
+      <c r="F101" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (83%)</t>
         </is>
       </c>
-      <c r="G88" s="13" t="inlineStr">
+      <c r="G101" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 10 vs ordered 300)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (83%) · Matching: brand, product name, form/spec · Not matching: pack size · price $14.00 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Pack quantity mismatch: ordered 300, page sells 10. · PACK MISMATCH — page is 10/pack but ordered 300/pack (30× off); different unit, routed to alternate</t>
-        </is>
-      </c>
-      <c r="H88" s="15" t="n">
+Web search (not in Price Match) · POSSIBLE (83%) · Matching: brand, product name, form/spec · Not matching: pack size · price $14.00 from page structured data (single offer) · Pack quantity mismatch: ordered 300, page sells 10. · PACK MISMATCH — page is 10/pack but ordered 300/pack (30× off); different unit, routed to alternate</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="n">
         <v>2.15</v>
       </c>
     </row>
-    <row r="89" ht="64" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
+    <row r="102" ht="64" customHeight="1">
+      <c r="A102" s="13" t="inlineStr">
         <is>
           <t>Criterion N300 Glove Ice Blue Nitrile M 300/Bx
 SKU: 1126831  ·  Schein price: $16.15/unit</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>3000 Medium Aurelia Sonic-300 Blue Nitrile 2.2 mil Powder Free Examination Gloves (10 Boxes)</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>myddssupply.com</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="n">
-        <v>159.99</v>
-      </c>
-      <c r="E89" s="12" t="inlineStr">
-        <is>
-          <t>https://myddssupply.com/products/3000-medium-aurelia-sonic-300-blue-nitrile-2-2-mil-powder-free-examination-gloves-10-boxes</t>
-        </is>
-      </c>
-      <c r="F89" s="10" t="inlineStr">
-        <is>
-          <t>POSSIBLE (47%)</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>PACK MISMATCH (page ? vs ordered 300) · VARIANT MISMATCH (ordered: Ice Blue Medium)
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>Aurelia Sonic Nitrile Exam Gloves: Small 300/Bx</t>
+        </is>
+      </c>
+      <c r="C102" s="14" t="inlineStr">
+        <is>
+          <t>net32.com</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="E102" s="16" t="inlineStr">
+        <is>
+          <t>https://www.net32.com/ec/aurelia-sonic-nitrile-exam-gloves-small-300-d-151428</t>
+        </is>
+      </c>
+      <c r="F102" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (35%)</t>
+        </is>
+      </c>
+      <c r="G102" s="13" t="inlineStr">
+        <is>
+          <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Ice Blue Medium)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (47%) · Matching: form/spec · Not matching: brand, product name, pack size · price $159.99 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Different brand and product line. No price found. · VARIANT MISMATCH — house-brand mismatch (ordered Criterion, page is a different brand); wrong variant, routed to alternate, VERIFY</t>
-        </is>
-      </c>
-      <c r="H89" s="10" t="inlineStr">
-        <is>
-          <t>Equiv $159.99 &gt; Schein $16.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="64" customHeight="1">
-      <c r="A90" s="13" t="inlineStr">
+Web search (not in Price Match) · POSSIBLE (35%) · Matching: pack size · Not matching: brand, product name, form/spec · price set from net32.com seller table: lowest available (incl. shipping) of 7 seller(s), via Lowest Price row · Brand and product name do not match. Variant size is also different. · VARIANT MISMATCH — house-brand mismatch (ordered Criterion, page is a different brand); wrong variant, routed to alternate, VERIFY · PRICE SUSPECT — locked $14.45 is far below the other sellers for this item (median $31.99); the seller-table parse may have caught a stray number, VERIFY</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="103" ht="64" customHeight="1">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t>Criterion N300 Glove Ice Blue Nitrile M 300/Bx
+SKU: 1126831  ·  Schein price: $16.15/unit</t>
+        </is>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>Nitrile Gloves 300 Pack</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>edmondsdentalsupply.com</t>
+        </is>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="E103" s="20" t="inlineStr">
+        <is>
+          <t>https://edmondsdentalsupply.com/product/nitrile-gloves-300-pack/</t>
+        </is>
+      </c>
+      <c r="F103" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (58%)</t>
+        </is>
+      </c>
+      <c r="G103" s="17" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Ice Blue Medium)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (58%) · Matching: form/spec, pack size · Not matching: brand, product name · Brand is not Criterion. Variant is 'Blue' not 'Ice Blue Medium'. Product name is generic 'Nitrile Gloves'. · VARIANT MISMATCH — house-brand mismatch (ordered Criterion, page is a different brand); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H103" s="19" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="104" ht="64" customHeight="1">
+      <c r="A104" s="13" t="inlineStr">
         <is>
           <t>Zirconia Pre-Polish Wheel Med Blue/Orange Ea
 SKU: 7013349  ·  Schein price: $52.86/unit</t>
         </is>
       </c>
-      <c r="B90" s="13" t="inlineStr">
+      <c r="B104" s="13" t="inlineStr">
         <is>
           <t>Diamond Polisher Wheel Medium Blue/Orange HP 2/Pk</t>
         </is>
       </c>
-      <c r="C90" s="14" t="inlineStr">
+      <c r="C104" s="14" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D90" s="15" t="n">
+      <c r="D104" s="15" t="n">
         <v>45.29</v>
       </c>
-      <c r="E90" s="16" t="inlineStr">
+      <c r="E104" s="16" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Diamond-Polisher-Wheel-Medium-Blue-Orange-HP-2-Pk</t>
         </is>
       </c>
-      <c r="F90" s="14" t="inlineStr">
+      <c r="F104" s="14" t="inlineStr">
         <is>
           <t>POSSIBLE (47%)</t>
         </is>
       </c>
-      <c r="G90" s="13" t="inlineStr">
+      <c r="G104" s="13" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 2 vs ordered ?) · VARIANT MISMATCH (ordered: Medium Blue/Orange)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (47%) · Matching: form/spec · Not matching: brand, product name, pack size · The ordered MPN DCA06-170-HP-BL/O does not match the page's MPN 194-9749M-110-HP-BL/O. The product name is also 'Diamond Polisher Wheel' instead of 'Zirconia Pre-Polish Wheel'.</t>
         </is>
       </c>
-      <c r="H90" s="15" t="n">
+      <c r="H104" s="15" t="n">
         <v>7.57</v>
       </c>
     </row>
-    <row r="91" ht="64" customHeight="1">
-      <c r="A91" s="17" t="inlineStr">
+    <row r="105" ht="64" customHeight="1">
+      <c r="A105" s="17" t="inlineStr">
         <is>
           <t>Zirconia Pre-Polish Wheel Med Blue/Orange Ea
 SKU: 7013349  ·  Schein price: $52.86/unit</t>
         </is>
       </c>
-      <c r="B91" s="17" t="inlineStr">
+      <c r="B105" s="17" t="inlineStr">
         <is>
           <t>Meisinger Twist Porcelain HP Polisher, Coarse, 17mm, Green, 2/Pk</t>
         </is>
       </c>
-      <c r="C91" s="18" t="inlineStr">
+      <c r="C105" s="18" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D91" s="19" t="n">
+      <c r="D105" s="19" t="n">
         <v>49.03</v>
       </c>
-      <c r="E91" s="20" t="inlineStr">
+      <c r="E105" s="20" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/meisinger-twist-porcelain-hp-polisher-coarse-17mm-d-183734</t>
         </is>
       </c>
-      <c r="F91" s="18" t="inlineStr">
+      <c r="F105" s="18" t="inlineStr">
         <is>
           <t>POSSIBLE (35%)</t>
         </is>
       </c>
-      <c r="G91" s="17" t="inlineStr">
+      <c r="G105" s="17" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 2 vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Medium Blue/Orange)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (35%) · Matching: brand · Not matching: product name, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 7 seller(s), via Lowest Price row · Product name 'Twist Porcelain HP Polisher' is different from 'Zirconia Pre-Polish Wheel'. Variant 'Green' and pack '2/Pk' do not match ordered 'Medium Blue/Orange' and 'None'. · VARIANT MISMATCH — color mismatch (ordered blue/orange, page green); wrong variant, routed to alternate, VERIFY</t>
         </is>
       </c>
-      <c r="H91" s="19" t="n">
+      <c r="H105" s="19" t="n">
         <v>3.83</v>
       </c>
     </row>
-    <row r="92" ht="64" customHeight="1">
-      <c r="A92" s="17" t="inlineStr">
+    <row r="106" ht="64" customHeight="1">
+      <c r="A106" s="17" t="inlineStr">
         <is>
           <t>Zirconia Pre-Polish Wheel Med Blue/Orange Ea
 SKU: 7013349  ·  Schein price: $52.86/unit</t>
         </is>
       </c>
-      <c r="B92" s="17" t="inlineStr">
+      <c r="B106" s="17" t="inlineStr">
         <is>
           <t>Mei Zirconia Pre-Polisher Handpiece Medium Wheel DCA06 Blue/Orange Refill Ea</t>
         </is>
       </c>
-      <c r="C92" s="18" t="inlineStr">
+      <c r="C106" s="18" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D92" s="19" t="n">
+      <c r="D106" s="19" t="n">
         <v>49.54</v>
       </c>
-      <c r="E92" s="20" t="inlineStr">
+      <c r="E106" s="20" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/mei-zirconia-pre-polisher-handpiece-medium-wheel-dca06-blue-orange-refill-ea-meisinger-usa-dca06-170-hp-bl-o</t>
         </is>
       </c>
-      <c r="F92" s="18" t="inlineStr">
+      <c r="F106" s="18" t="inlineStr">
         <is>
           <t>POSSIBLE (23%)</t>
         </is>
       </c>
-      <c r="G92" s="17" t="inlineStr">
+      <c r="G106" s="17" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (23%) · Matching: product name · Not matching: brand, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 1 seller(s), via min of Total column · No pricing information found on the page.</t>
         </is>
       </c>
-      <c r="H92" s="19" t="n">
+      <c r="H106" s="19" t="n">
         <v>3.32</v>
       </c>
     </row>
-    <row r="93" ht="64" customHeight="1">
-      <c r="A93" s="9" t="inlineStr">
+    <row r="107" ht="64" customHeight="1">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>Zirconia Pre-Polish Wheel Med Blue/Orange Ea
 SKU: 7013349  ·  Schein price: $52.86/unit</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
+      <c r="B107" s="9" t="inlineStr">
         <is>
           <t>#DCA05-110 Blue/Orange Polisher Small Wheel HP Pack of 2</t>
         </is>
       </c>
-      <c r="C93" s="10" t="inlineStr">
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>shop.benco.com</t>
         </is>
       </c>
-      <c r="D93" s="11" t="n">
+      <c r="D107" s="11" t="n">
         <v>55.49</v>
       </c>
-      <c r="E93" s="12" t="inlineStr">
+      <c r="E107" s="12" t="inlineStr">
         <is>
           <t>https://shop.benco.com/Product/4480-475/dca05-110-blueorange-polisher-small-wheel-hp-pack-</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F107" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (47%)</t>
         </is>
       </c>
-      <c r="G93" s="9" t="inlineStr">
+      <c r="G107" s="9" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 2 vs ordered ?) · VARIANT MISMATCH (ordered: Medium Blue/Orange)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (47%) · Matching: form/spec · Not matching: brand, product name, pack size · The ordered MPN DCA06-170-HP-BL/O does not match the page's MPN DCA05-110-HP-BL/O. The product name is also 'Polisher Small Wheel' instead of 'Zirconia Pre-Polish Wheel'.</t>
         </is>
       </c>
-      <c r="H93" s="10" t="inlineStr">
+      <c r="H107" s="10" t="inlineStr">
         <is>
           <t>Equiv $55.49 &gt; Schein $52.86</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="64" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="108" ht="64" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>Zirconia Pre-Polish Wheel Med Blue/Orange Ea
 SKU: 7013349  ·  Schein price: $52.86/unit</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
         <is>
           <t>Universal Extraoral Shaping and Polishing Kit, According to Dentsply Sirona - DSU21</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>avtecdental.com</t>
         </is>
       </c>
-      <c r="D94" s="7" t="n">
+      <c r="D108" s="7" t="n">
         <v>577.1</v>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>https://www.avtecdental.com/products/universal-extraoral-shaping-and-polishing-kit-according-to-dentsply-sirona-dsu21</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (20%)</t>
         </is>
       </c>
-      <c r="G94" s="5" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 1 vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Medium Blue/Orange)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (20%) · Not matching: brand, product name, form/spec, pack size · The ordered product is a single Zirconia Pre-Polish Wheel, not a kit. The MPN also does not match.</t>
         </is>
       </c>
-      <c r="H94" s="6" t="inlineStr">
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>Equiv $577.10 &gt; Schein $52.86</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="64" customHeight="1">
-      <c r="A95" s="9" t="inlineStr">
+    <row r="109" ht="64" customHeight="1">
+      <c r="A109" s="9" t="inlineStr">
         <is>
           <t>Zirconia Pre-Polish Wheel Med Blue/Orange Ea
 SKU: 7013349  ·  Schein price: $52.86/unit</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B109" s="9" t="inlineStr">
         <is>
           <t>Universal Extraoral Shaping and Polishing Kit, According to Dentsply Complete System REFILL - DSU21AR</t>
         </is>
       </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="C109" s="10" t="inlineStr">
         <is>
           <t>avtecdental.com</t>
         </is>
       </c>
-      <c r="D95" s="11" t="n">
+      <c r="D109" s="11" t="n">
         <v>910.2</v>
       </c>
-      <c r="E95" s="12" t="inlineStr">
+      <c r="E109" s="12" t="inlineStr">
         <is>
           <t>https://www.avtecdental.com/products/universal-extraoral-shaping-and-polishing-kit-according-to-dentsply-complete-system-refill-dsu21ar</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F109" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (20%)</t>
         </is>
       </c>
-      <c r="G95" s="9" t="inlineStr">
+      <c r="G109" s="9" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 1 vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Medium Blue/Orange)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (20%) · Not matching: brand, product name, form/spec, pack size · The ordered product is a single Zirconia Pre-Polish Wheel, not a kit. The MPN also does not match.</t>
         </is>
       </c>
-      <c r="H95" s="10" t="inlineStr">
+      <c r="H109" s="10" t="inlineStr">
         <is>
           <t>Equiv $910.20 &gt; Schein $52.86</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="64" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
+    <row r="110" ht="64" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9742M-040 2/Pk
 SKU: 7013185  ·  Schein price: $47.55/unit</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B110" s="5" t="inlineStr">
         <is>
           <t>Diamond Polisher Flame RA Red/Orange 2/Pk</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D96" s="7" t="n">
+      <c r="D110" s="7" t="n">
         <v>45.49</v>
       </c>
-      <c r="E96" s="8" t="inlineStr">
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Meisinger-Polishers-9743F-040-RA-R-O</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (79%)</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G110" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: specified)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (79%) · Matching: brand, form/spec, pack size · Not matching: product name · Product name and MPN mismatch. Ordered 'Polisher HP' (MPN 9742M-040-HP-BL/O), page is 'Diamond Polisher Flame RA Red/Orange' (MPN 194-9743F-040-RA-R/O).</t>
         </is>
       </c>
-      <c r="H96" s="7" t="n">
+      <c r="H110" s="7" t="n">
         <v>2.06</v>
       </c>
     </row>
-    <row r="97" ht="64" customHeight="1">
-      <c r="A97" s="9" t="inlineStr">
+    <row r="111" ht="64" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9742M-040 2/Pk
 SKU: 7013185  ·  Schein price: $47.55/unit</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
+      <c r="B111" s="9" t="inlineStr">
         <is>
           <t>Meisinger HP #9742F.040 Fine, Point Shaped, Diamond Impregnated Polisher, Red, 2/Pk</t>
         </is>
       </c>
-      <c r="C97" s="10" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D97" s="11" t="n">
+      <c r="D111" s="11" t="n">
         <v>48.3</v>
       </c>
-      <c r="E97" s="12" t="inlineStr">
+      <c r="E111" s="12" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/meisinger-hp-9742f040-fine-point-shaped-diamond-d-189688</t>
         </is>
       </c>
-      <c r="F97" s="10" t="inlineStr">
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (88%)</t>
         </is>
       </c>
-      <c r="G97" s="9" t="inlineStr">
+      <c r="G111" s="9" t="inlineStr">
         <is>
           <t>POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (88%) · Matching: brand, product name, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 1 seller(s), via Lowest Price row · MPN mismatch: ordered 9742M-040-HP-BL/O, page is 9742F.040. Variant mismatch: ordered 'None', page is 'Red'.</t>
         </is>
       </c>
-      <c r="H97" s="10" t="inlineStr">
+      <c r="H111" s="10" t="inlineStr">
         <is>
           <t>Equiv $48.30 &gt; Schein $47.55</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="64" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
+    <row r="112" ht="64" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9742M-040 2/Pk
 SKU: 7013185  ·  Schein price: $47.55/unit</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B112" s="5" t="inlineStr">
         <is>
           <t>Meisinger HP #DCA04.040 Pre-Polish, Point Shaped, Diamond Impregnated Polisher, Blue, 2/Pk</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D98" s="7" t="n">
+      <c r="D112" s="7" t="n">
         <v>50.95</v>
       </c>
-      <c r="E98" s="8" t="inlineStr">
+      <c r="E112" s="8" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/meisinger-hp-dca04040-prepolish-point-shaped-diamond-d-189736?vid=130&amp;frt=37</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (88%)</t>
         </is>
       </c>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G112" s="5" t="inlineStr">
         <is>
           <t>POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (88%) · Matching: brand, product name, form/spec, pack size · price set from net32.com seller table: lowest available (incl. shipping) of 1 seller(s), via Lowest Price row · MPN mismatch: ordered 9742M-040-HP-BL/O, page is DCA04.040. Variant mismatch: ordered 'None', page is 'Blue'.</t>
         </is>
       </c>
-      <c r="H98" s="6" t="inlineStr">
+      <c r="H112" s="6" t="inlineStr">
         <is>
           <t>Equiv $50.95 &gt; Schein $47.55</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="64" customHeight="1">
-      <c r="A99" s="9" t="inlineStr">
+    <row r="113" ht="64" customHeight="1">
+      <c r="A113" s="13" t="inlineStr">
         <is>
           <t>Oral-B Glide Floss Deep Clean 4 meter Mint 72/Bx
 SKU: 3250498  ·  Schein price: $50.99/unit</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>Reach Total Care Floss-Clean Toothbrush - Adult Soft 72/Pk</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>surgimac.com</t>
-        </is>
-      </c>
-      <c r="D99" s="11" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="E99" s="12" t="inlineStr">
-        <is>
-          <t>https://surgimac.com/products/reach-total-care-floss-clean-toothbrush-adult-soft-72-pk</t>
-        </is>
-      </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>POSSIBLE (32%)</t>
-        </is>
-      </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>PACK MISMATCH (page ? vs ordered 72) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Mint)
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Healthy Gums Floss Refill 160m 2/Bx Unflavored</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>crazydentalprices.com</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="E113" s="16" t="inlineStr">
+        <is>
+          <t>https://www.crazydentalprices.com/Pro-Health-Glide-Floss-Procter-Gamble-80779742</t>
+        </is>
+      </c>
+      <c r="F113" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (51%)</t>
+        </is>
+      </c>
+      <c r="G113" s="13" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page 2 vs ordered 72) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Mint)
 POSSIBLE — related product, requires client review before acting
-Web search (not in Price Match) · POSSIBLE (32%) · Not matching: brand, product name, form/spec, pack size · price $52.98 via free HTTP fetch (page structured data — 0 Firecrawl credits) · Product is a toothbrush, not dental floss. No price found on page.</t>
-        </is>
-      </c>
-      <c r="H99" s="10" t="inlineStr">
-        <is>
-          <t>Equiv $52.98 &gt; Schein $50.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="64" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
+Web search (not in Price Match) · POSSIBLE (51%) · Matching: brand · Not matching: product name, form/spec, pack size · Product name, size, variant, and pack quantity do not match the order. Ordered 'Glide Floss Deep Clean 4 meter Mint 72/Bx', page is 'Glide Healthy Gums Floss Refill 160m 2/Bx Unflavored'. · VARIANT MISMATCH — flavor mismatch (ordered 'mint', page 'unflavored'); wrong variant, routed to alternate, VERIFY · PACK MISMATCH — page is 2/pack but ordered 72/pack (36× off); different unit, routed to alternate · PRICE UNRELIABLE — $11.25 is far below the other sources for this item (median $48.17); likely a related-item or single-unit price, VERIFY MANUALLY</t>
+        </is>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>39.74</v>
+      </c>
+    </row>
+    <row r="114" ht="64" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>Sharps Cont Counter Balanced 3 Gal RD Ea
 SKU: 9872474  ·  Schein price: $17.42/unit</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B114" s="5" t="inlineStr">
         <is>
           <t>BD Sharps Collector 3 gallon Sharps Collector, Next Generation, Horizontal</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D100" s="7" t="n">
+      <c r="D114" s="7" t="n">
         <v>18.5</v>
       </c>
-      <c r="E100" s="8" t="inlineStr">
+      <c r="E114" s="8" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/bd-sharps-collector-3-gallon-next-generation-d-114715</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (50%)</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: Red)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (50%) · Matching: form/spec, pack size · Not matching: brand, product name · price set from net32.com seller table: lowest available (incl. shipping) of 2 seller(s), via Lowest Price row · Page is for 'BD Sharps Collector', not 'Sharps Container Counter Balanced'. Price not found on page.</t>
         </is>
       </c>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="H114" s="6" t="inlineStr">
         <is>
           <t>Equiv $18.50 &gt; Schein $17.42</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="64" customHeight="1">
-      <c r="A101" s="9" t="inlineStr">
+    <row r="115" ht="64" customHeight="1">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>Sharps Cont Counter Balanced 3 Gal RD Ea
 SKU: 9872474  ·  Schein price: $17.42/unit</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
+      <c r="B115" s="9" t="inlineStr">
         <is>
           <t>Sharps Collectors, 3 Gallon, Red</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D101" s="11" t="n">
+      <c r="D115" s="11" t="n">
         <v>154.67</v>
       </c>
-      <c r="E101" s="12" t="inlineStr">
+      <c r="E115" s="12" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/sharps-collectors-3-gallon-red-crosstex-305436</t>
         </is>
       </c>
-      <c r="F101" s="10" t="inlineStr">
+      <c r="F115" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (80%)</t>
         </is>
       </c>
-      <c r="G101" s="9" t="inlineStr">
+      <c r="G115" s="9" t="inlineStr">
         <is>
           <t>POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (80%) · Matching: brand, product name, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 1 seller(s), via min of Total column · Page is for 'Sharps Collectors' by Crosstex, not 'Sharps Container Counter Balanced'. Price not found on page.</t>
         </is>
       </c>
-      <c r="H101" s="10" t="inlineStr">
+      <c r="H115" s="10" t="inlineStr">
         <is>
           <t>Equiv $154.67 &gt; Schein $17.42</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="64" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="116" ht="64" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>Sharps Cont Counter Balanced 3 Gal RD Ea
 SKU: 9872474  ·  Schein price: $17.42/unit</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>BD Multi-purpose Sharps Container, 16-3/5 x 10-7/10 x 6 Inch</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>lexiconsupply.com</t>
         </is>
       </c>
-      <c r="D102" s="7" t="n">
+      <c r="D116" s="7" t="n">
         <v>179.99</v>
       </c>
-      <c r="E102" s="8" t="inlineStr">
+      <c r="E116" s="8" t="inlineStr">
         <is>
           <t>https://www.lexiconsupply.com/products/bd-multi-purpose-sharps-container-16-3-5-x-10-7-10-x-6-inch</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (43%)</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G116" s="5" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page ? vs ordered ?) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: Red)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (43%) · Matching: brand · Not matching: product name, form/spec, pack size · Product name and size/form do not match the order. The page lists the MPN but the product description is different. The variant is also not specified as 'Red' and the item is out of stock.</t>
         </is>
       </c>
-      <c r="H102" s="6" t="inlineStr">
+      <c r="H116" s="6" t="inlineStr">
         <is>
           <t>Equiv $179.99 &gt; Schein $17.42</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="64" customHeight="1">
-      <c r="A103" s="9" t="inlineStr">
+    <row r="117" ht="64" customHeight="1">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>ReSURGE Inst Cleaning Solution 33oz/Bt
 SKU: 3120114  ·  Schein price: $91.15/unit</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B117" s="9" t="inlineStr">
         <is>
           <t>ReSURGE Instrument Cleaning Solution, 33.8oz (1L), #21521</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C117" s="10" t="inlineStr">
         <is>
           <t>supplydoc.com</t>
         </is>
       </c>
-      <c r="D103" s="11" t="n">
+      <c r="D117" s="11" t="n">
         <v>102.99</v>
       </c>
-      <c r="E103" s="12" t="inlineStr">
+      <c r="E117" s="12" t="inlineStr">
         <is>
           <t>https://supplydoc.com/products/resurge-instrument-cleaning-solution-33-8oz-1l-21521</t>
         </is>
       </c>
-      <c r="F103" s="10" t="inlineStr">
+      <c r="F117" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (98%)</t>
         </is>
       </c>
-      <c r="G103" s="9" t="inlineStr">
+      <c r="G117" s="9" t="inlineStr">
         <is>
           <t>POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (98%) · Matching: brand, product name, form/spec, pack size · Product is out of stock. Size 33.8oz is considered a match for 33oz. MPN 21521 matches.</t>
         </is>
       </c>
-      <c r="H103" s="10" t="inlineStr">
+      <c r="H117" s="10" t="inlineStr">
         <is>
           <t>Equiv $102.99 &gt; Schein $91.15</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="64" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="118" ht="64" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
 SKU: 1403081  ·  Schein price: $9.59/unit</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Disinfectant Wipes 6"x 6.75", 160/Can - Metrex 14-1100</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D104" s="7" t="n">
+      <c r="D118" s="7" t="n">
         <v>18.39</v>
       </c>
-      <c r="E104" s="8" t="inlineStr">
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/caviwipes-2-0-disinfectant-wipes-6-x-6-75-160-can-metrex-14-1100-1</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (80%)</t>
         </is>
       </c>
-      <c r="G104" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (80%) · Matching: brand, product name, form/spec, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 1 seller(s), via min of Total column · No pricing information found on the page. The page describes how their algorithm works but does not show any actual seller offers or prices.</t>
         </is>
       </c>
-      <c r="H104" s="6" t="inlineStr">
+      <c r="H118" s="6" t="inlineStr">
         <is>
           <t>Equiv $18.39 &gt; Schein $9.59</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="64" customHeight="1">
-      <c r="A105" s="9" t="inlineStr">
+    <row r="119" ht="64" customHeight="1">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
 SKU: 1403081  ·  Schein price: $9.59/unit</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
+      <c r="B119" s="9" t="inlineStr">
         <is>
           <t>CaviWipes 2.0 Large 160/Can x 12/Cs</t>
         </is>
       </c>
-      <c r="C105" s="10" t="inlineStr">
+      <c r="C119" s="10" t="inlineStr">
         <is>
           <t>curio.dental</t>
         </is>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="D119" s="11" t="n">
         <v>161.1</v>
       </c>
-      <c r="E105" s="12" t="inlineStr">
+      <c r="E119" s="12" t="inlineStr">
         <is>
           <t>https://curio.dental/products/caviwipes-2-0-large-160-can-x-12-cs</t>
         </is>
       </c>
-      <c r="F105" s="10" t="inlineStr">
+      <c r="F119" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (68%)</t>
         </is>
       </c>
-      <c r="G105" s="9" t="inlineStr">
+      <c r="G119" s="9" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 160 vs ordered 160) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (68%) · Matching: brand, product name · Not matching: form/spec, pack size · The page sells a case of 12 cans, not a single can. The ordered size/form is 6"x6.75", but the page only specifies 'Large' without dimensions.</t>
         </is>
       </c>
-      <c r="H105" s="10" t="inlineStr">
+      <c r="H119" s="10" t="inlineStr">
         <is>
           <t>Equiv $161.10 &gt; Schein $9.59</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="64" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
+    <row r="120" ht="64" customHeight="1">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>Fuji II LC Capsules A3.5 48/Bx
+SKU: 3333468  ·  Schein price: $372.66/unit</t>
+        </is>
+      </c>
+      <c r="B120" s="13" t="inlineStr"/>
+      <c r="C120" s="14" t="inlineStr">
+        <is>
+          <t>frontierdental.com</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="n">
+        <v>235.18</v>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>https://frontierdental.com/us/en/product/fuji-ii-lc-glass-ionomer-restorative-light-cure-capsules-refill-0-1-ml-a3-5-48-pk-36413?bp=ZnJvbnRpZXJkZW50YWw%3D&amp;ctr=VVM%3D</t>
+        </is>
+      </c>
+      <c r="F120" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G120" s="13" t="inlineStr">
+        <is>
+          <t>PACK MISMATCH (page ? vs ordered 48) · SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: A3.5)
+POSSIBLE — related product, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · Not matching: brand, product name, form/spec, pack size · price $235.18 from page structured data (single offer) · Page content is truncated and does not contain product details or pricing.</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>137.48</v>
+      </c>
+    </row>
+    <row r="121" ht="64" customHeight="1">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
 SKU: 3120212  ·  Schein price: $36.80/unit</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="B121" s="9" t="inlineStr">
         <is>
           <t>Genie VPS Rapid Set Light Body Bulk Kit 50mL 60/Box</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C121" s="10" t="inlineStr">
         <is>
           <t>supplyclinic.com</t>
         </is>
       </c>
-      <c r="D106" s="7" t="n">
+      <c r="D121" s="11" t="n">
         <v>702.27</v>
       </c>
-      <c r="E106" s="8" t="inlineStr">
+      <c r="E121" s="12" t="inlineStr">
         <is>
           <t>https://www.supplyclinic.com/items/genie-vps-rapid-set-light-body-bulk-kit-50ml-60-box-sultan-healthcare-77720</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr">
+      <c r="F121" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (54%)</t>
         </is>
       </c>
-      <c r="G106" s="5" t="inlineStr">
+      <c r="G121" s="9" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 60 vs ordered 2) · VARIANT MISMATCH (ordered: XLight Body)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (54%) · Matching: brand, form/spec · Not matching: product name, pack size · price set from supplyclinic.com seller table: lowest available (incl. shipping) of 5 seller(s), via min of Total column · Pack quantity is 60, not 2. Variant is 'Light Body' not 'XLight Body'. · PACK MISMATCH — page is 60/pack but ordered 2/pack (30× off); different unit, routed to alternate</t>
         </is>
       </c>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="H121" s="10" t="inlineStr">
         <is>
           <t>Equiv $702.27 &gt; Schein $36.80</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="64" customHeight="1">
-      <c r="A107" s="9" t="inlineStr">
+    <row r="122" ht="64" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
 SKU: 3120212  ·  Schein price: $36.80/unit</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>Sultan Genie VPS Impression Materials Bulk Kit Light Body Fast Set 50ml 60 Count</t>
         </is>
       </c>
-      <c r="C107" s="10" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>medentrx.com</t>
         </is>
       </c>
-      <c r="D107" s="11" t="n">
+      <c r="D122" s="7" t="n">
         <v>999.99</v>
       </c>
-      <c r="E107" s="12" t="inlineStr">
+      <c r="E122" s="8" t="inlineStr">
         <is>
           <t>https://medentrx.com/sultan-genie-vps-impression-materials-bulk-kit-light-body-regular-set-50ml-60-count-30796/</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (58%)</t>
         </is>
       </c>
-      <c r="G107" s="9" t="inlineStr">
+      <c r="G122" s="5" t="inlineStr">
         <is>
           <t>PACK MISMATCH (page 60 vs ordered 2) · VARIANT MISMATCH (ordered: XLight Body)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (58%) · Matching: brand, form/spec · Not matching: product name, pack size · Product is 'Fast Set' not 'Rapid Set' and pack quantity is 60, not 2. Variant is 'Light Body Fast Set' not 'XLight Body'. · PACK MISMATCH — page is 60/pack but ordered 2/pack (30× off); different unit, routed to alternate</t>
         </is>
       </c>
-      <c r="H107" s="10" t="inlineStr">
+      <c r="H122" s="6" t="inlineStr">
         <is>
           <t>Equiv $999.99 &gt; Schein $36.80</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="64" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
+    <row r="123" ht="64" customHeight="1">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>Diamond FG Coarse 841G-012 5/Pk
 SKU: 7011085  ·  Schein price: $43.65/unit</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="B123" s="9" t="inlineStr">
         <is>
           <t>Meisinger Diamonds 841-012-FG Medium 5/Pk</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D108" s="7" t="n">
+      <c r="D123" s="11" t="n">
         <v>53.95</v>
       </c>
-      <c r="E108" s="8" t="inlineStr">
+      <c r="E123" s="12" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Meisinger-Diamonds-800-841-012-FG?leadsource=Jolt_CDP</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
+      <c r="F123" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (77%)</t>
         </is>
       </c>
-      <c r="G108" s="5" t="inlineStr">
+      <c r="G123" s="9" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: 841G-012)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (77%) · Matching: brand, form/spec, pack size · Not matching: product name · The ordered variant is 'Diamond FG Coarse 841G-012'. The page lists 'Meisinger Diamonds 841-012-FG Medium 5/Pk'. The brand 'Meisinger' matches. The pack quantity of 5 matches. However, the ordered variant '841G-012' (Coarse) does not match the page's '841-012-FG Medium'. The 'G' in the ordered variant indicates 'Coarse', while the page explicitly states 'Medium' and lacks the 'G'. This is a variant mismatch, making name_match=false and match_type=rejected.</t>
         </is>
       </c>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="H123" s="10" t="inlineStr">
         <is>
           <t>Equiv $53.95 &gt; Schein $43.65</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="64" customHeight="1">
-      <c r="A109" s="9" t="inlineStr">
+    <row r="124" ht="64" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>Diamond FG Coarse 841G-012 5/Pk
 SKU: 7011085  ·  Schein price: $43.65/unit</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
+      <c r="B124" s="5" t="inlineStr">
         <is>
           <t>Meisinger Diamonds 841G-014-FG Coarse 5/Pk</t>
         </is>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C124" s="6" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D109" s="11" t="n">
+      <c r="D124" s="7" t="n">
         <v>53.95</v>
       </c>
-      <c r="E109" s="12" t="inlineStr">
+      <c r="E124" s="8" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Meisinger-Diamonds-800-841G-014-FG</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <t>POSSIBLE (66%)</t>
         </is>
       </c>
-      <c r="G109" s="9" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>VARIANT MISMATCH (ordered: 841G-012)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (66%) · Matching: form/spec, pack size · Not matching: brand, product name · The ordered variant is 841G-012, but the page sells 841G-014-FG. This is a different product.</t>
         </is>
       </c>
-      <c r="H109" s="10" t="inlineStr">
+      <c r="H124" s="6" t="inlineStr">
         <is>
           <t>Equiv $53.95 &gt; Schein $43.65</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="64" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
+    <row r="125" ht="64" customHeight="1">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>Diamond FG Coarse 841G-012 5/Pk
 SKU: 7011085  ·  Schein price: $43.65/unit</t>
         </is>
       </c>
-      <c r="B110" s="5" t="inlineStr">
+      <c r="B125" s="9" t="inlineStr">
         <is>
           <t>NTI Diamond Burs FG, Barrel, 5/Pkg (Kerr Rotary)</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>skydentalsupply.com</t>
         </is>
       </c>
-      <c r="D110" s="7" t="n">
+      <c r="D125" s="11" t="n">
         <v>105.99</v>
       </c>
-      <c r="E110" s="8" t="inlineStr">
+      <c r="E125" s="12" t="inlineStr">
         <is>
           <t>https://www.skydentalsupply.com/nti-diamond-burs%E2%80%93fg-coarse-barrel-flat-end.htm</t>
         </is>
       </c>
-      <c r="F110" s="6" t="inlineStr">
+      <c r="F125" s="10" t="inlineStr">
         <is>
           <t>POSSIBLE (43%)</t>
         </is>
       </c>
-      <c r="G110" s="5" t="inlineStr">
+      <c r="G125" s="9" t="inlineStr">
         <is>
           <t>SIZE/VOLUME MISMATCH (e.g. 2L vs 5L) — verify on page · VARIANT MISMATCH (ordered: 841G-012)
 POSSIBLE — related product, requires client review before acting
 Web search (not in Price Match) · POSSIBLE (43%) · Matching: pack size · Not matching: brand, product name, form/spec · Product is NTI brand, not generic. Variant C811-047 does not match ordered 841G-012. MPN C845KR-018 does not match ordered 841G-012-FG.</t>
         </is>
       </c>
-      <c r="H110" s="6" t="inlineStr">
+      <c r="H125" s="10" t="inlineStr">
         <is>
           <t>Equiv $105.99 &gt; Schein $43.65</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="64" customHeight="1">
-      <c r="A111" s="9" t="inlineStr">
+    <row r="126" ht="64" customHeight="1">
+      <c r="A126" s="17" t="inlineStr">
         <is>
           <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk
 SKU: 8889527  ·  Schein price: $71.70/unit</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>darbydental.com</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="n"/>
-      <c r="E111" s="12" t="inlineStr">
-        <is>
-          <t>https://www.darbydental.com/9062590.html</t>
-        </is>
-      </c>
-      <c r="F111" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H111" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="64" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="B126" s="17" t="inlineStr"/>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>orthazone.com</t>
+        </is>
+      </c>
+      <c r="D126" s="19" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="E126" s="20" t="inlineStr">
+        <is>
+          <t>https://www.orthazone.com/209-fdt-part-fiber-lux-posts-refill-45-blue-6168</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G126" s="17" t="inlineStr">
+        <is>
+          <t>VARIANT MISMATCH (ordered: Red)
+POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · skipped — page too large to be a product listing (category/search page) · VARIANT MISMATCH — color mismatch (ordered red, page blue); wrong variant, routed to alternate, VERIFY</t>
+        </is>
+      </c>
+      <c r="H126" s="19" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="127" ht="64" customHeight="1">
+      <c r="A127" s="13" t="inlineStr">
+        <is>
+          <t>Oral-B Glide Floss Deep Clean 4 meter Mint 72/Bx
+SKU: 3250498  ·  Schein price: $50.99/unit</t>
+        </is>
+      </c>
+      <c r="B127" s="13" t="inlineStr"/>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>orthazone.com</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="E127" s="16" t="inlineStr">
+        <is>
+          <t>https://www.orthazone.com/209-fdt-glide-floss-pro-heah-original-4m-72cs-6265</t>
+        </is>
+      </c>
+      <c r="F127" s="14" t="inlineStr">
+        <is>
+          <t>POSSIBLE (0%)</t>
+        </is>
+      </c>
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>POSSIBLE — unverified listing, requires client review before acting
+Web search (not in Price Match) · POSSIBLE (0%) · skipped — page too large to be a product listing (category/search page)</t>
+        </is>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="128" ht="64" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk
 SKU: 8889527  ·  Schein price: $71.70/unit</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>safcodental.com</t>
         </is>
       </c>
-      <c r="D112" s="6" t="n"/>
-      <c r="E112" s="8" t="inlineStr">
+      <c r="D128" s="6" t="n"/>
+      <c r="E128" s="8" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/product/parapost-reg-fiber-lux</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G112" s="5" t="inlineStr">
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H112" s="6" t="inlineStr">
+      <c r="H128" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="64" customHeight="1">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk
-SKU: 8889527  ·  Schein price: $71.70/unit</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C113" s="10" t="inlineStr">
-        <is>
-          <t>orthazone.com</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>https://www.orthazone.com/209-fdt-part-fiber-lux-posts-refill-45-blue-6168</t>
-        </is>
-      </c>
-      <c r="F113" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G113" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H113" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="64" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk
-SKU: 8889527  ·  Schein price: $71.70/unit</t>
-        </is>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>darbydental.com</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="8" t="inlineStr">
-        <is>
-          <t>https://www.darbydental.com/9062584.html</t>
-        </is>
-      </c>
-      <c r="F114" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="64" customHeight="1">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>ParaPost Fiber Lux Red PF171-5.0 5/Pk
-SKU: 8889527  ·  Schein price: $71.70/unit</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C115" s="10" t="inlineStr">
-        <is>
-          <t>pattersondental.com</t>
-        </is>
-      </c>
-      <c r="D115" s="10" t="n"/>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/en-CA/Supplies/pins-posts/posts-metal-free/parapost-fiber-lux-translucent-fiber-posts-system-refills/PIF_69852</t>
-        </is>
-      </c>
-      <c r="F115" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H115" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="64" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
+    <row r="129" ht="64" customHeight="1">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>Mity K-Files 25mm #10 6/Pk
 SKU: 2013820  ·  Schein price: $25.40/unit</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="B129" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
+      <c r="C129" s="10" t="inlineStr">
         <is>
           <t>safcodental.com</t>
         </is>
       </c>
-      <c r="D116" s="6" t="n"/>
-      <c r="E116" s="8" t="inlineStr">
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="12" t="inlineStr">
         <is>
           <t>https://www.safcodental.com/product/kerr-k-files-sup-trade-sup</t>
         </is>
       </c>
-      <c r="F116" s="6" t="inlineStr">
+      <c r="F129" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G116" s="5" t="inlineStr">
+      <c r="G129" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H116" s="6" t="inlineStr">
+      <c r="H129" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="64" customHeight="1">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>Mity K-Files 25mm #10 6/Pk
-SKU: 2013820  ·  Schein price: $25.40/unit</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C117" s="10" t="inlineStr">
-        <is>
-          <t>midwestdental.com</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="n"/>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>https://midwestdental.com/k-files/_item/k-files-kerr-endodontics-25mm-length-files-70-25mm-6pkg</t>
-        </is>
-      </c>
-      <c r="F117" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H117" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="64" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+    <row r="130" ht="64" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B130" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>pattersondental.com</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="n"/>
-      <c r="E118" s="8" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/071272137</t>
-        </is>
-      </c>
-      <c r="F118" s="6" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>ddsdentalsupplies.com</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="n"/>
+      <c r="E130" s="8" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/face-masks/</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G130" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H118" s="6" t="inlineStr">
+      <c r="H130" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="64" customHeight="1">
-      <c r="A119" s="9" t="inlineStr">
+    <row r="131" ht="64" customHeight="1">
+      <c r="A131" s="9" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B119" s="9" t="inlineStr">
+      <c r="B131" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C119" s="10" t="inlineStr">
-        <is>
-          <t>ddsdentalsupplies.com</t>
-        </is>
-      </c>
-      <c r="D119" s="10" t="n"/>
-      <c r="E119" s="12" t="inlineStr">
-        <is>
-          <t>https://ddsdentalsupplies.com/face-masks/</t>
-        </is>
-      </c>
-      <c r="F119" s="10" t="inlineStr">
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>supplydoc.com</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>https://supplydoc.com/products/s3-level-3-earloop-face-masks-50-box</t>
+        </is>
+      </c>
+      <c r="F131" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G119" s="9" t="inlineStr">
+      <c r="G131" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H119" s="10" t="inlineStr">
+      <c r="H131" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="64" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
+    <row r="132" ht="64" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>S3+ Face Masks L3 Black 50/Bx
 SKU: 1392761  ·  Schein price: $9.55/unit</t>
         </is>
       </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="B132" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>supplydoc.com</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="n"/>
-      <c r="E120" s="8" t="inlineStr">
-        <is>
-          <t>https://supplydoc.com/products/s3-level-3-earloop-face-masks-50-box</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>optimusdentalsupply.com</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="n"/>
+      <c r="E132" s="8" t="inlineStr">
+        <is>
+          <t>https://optimusdentalsupply.com/face-masks/cranberry-masks/cranberry-s3-skin-health-level-3-face-mask-black-50-bx/</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G120" s="5" t="inlineStr">
+      <c r="G132" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H120" s="6" t="inlineStr">
+      <c r="H132" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="64" customHeight="1">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>S3+ Face Masks L3 Black 50/Bx
-SKU: 1392761  ·  Schein price: $9.55/unit</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
-        <is>
-          <t>optimusdentalsupply.com</t>
-        </is>
-      </c>
-      <c r="D121" s="10" t="n"/>
-      <c r="E121" s="12" t="inlineStr">
-        <is>
-          <t>https://optimusdentalsupply.com/face-masks/cranberry-masks/cranberry-s3-skin-health-level-3-face-mask-black-50-bx/</t>
-        </is>
-      </c>
-      <c r="F121" s="10" t="inlineStr">
+    <row r="133" ht="64" customHeight="1">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>Mixing Tips Reﬁll Teal 50mL 48/Bx
+SKU: 2223852  ·  Schein price: $70.13/unit</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>Mixing Tips for 50 ml Cartridges – Teal, 48/Pkg</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>pattersondental.com</t>
+        </is>
+      </c>
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>https://www.pattersondental.com/Supplies/ItemDetail/071806793</t>
+        </is>
+      </c>
+      <c r="F133" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G121" s="9" t="inlineStr">
+      <c r="G133" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H121" s="10" t="inlineStr">
+      <c r="H133" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="64" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
+    <row r="134" ht="64" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk
 SKU: 2222660  ·  Schein price: $76.60/unit</t>
         </is>
       </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="B134" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>surgimac.com</t>
         </is>
       </c>
-      <c r="D122" s="6" t="n"/>
-      <c r="E122" s="8" t="inlineStr">
+      <c r="D134" s="6" t="n"/>
+      <c r="E134" s="8" t="inlineStr">
         <is>
           <t>https://surgimac.com/products/mark3-crown-and-bridge-mixing-tips-10-1-25-pk</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G122" s="5" t="inlineStr">
+      <c r="G134" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H122" s="6" t="inlineStr">
+      <c r="H134" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="64" customHeight="1">
-      <c r="A123" s="9" t="inlineStr">
+    <row r="135" ht="64" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk
 SKU: 2222660  ·  Schein price: $76.60/unit</t>
         </is>
       </c>
-      <c r="B123" s="9" t="inlineStr">
+      <c r="B135" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C123" s="10" t="inlineStr">
-        <is>
-          <t>pattersondental.com</t>
-        </is>
-      </c>
-      <c r="D123" s="10" t="n"/>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/071808278</t>
-        </is>
-      </c>
-      <c r="F123" s="10" t="inlineStr">
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>optimusdentalsupply.com</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="n"/>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>https://optimusdentalsupply.com/kerr-mixing-tips-small-yellow-48-pk/</t>
+        </is>
+      </c>
+      <c r="F135" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G123" s="9" t="inlineStr">
+      <c r="G135" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H123" s="10" t="inlineStr">
+      <c r="H135" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="64" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>Dynamic Mixing Tips Yellow w/LuerLock 40/Pk
-SKU: 2222660  ·  Schein price: $76.60/unit</t>
-        </is>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>optimusdentalsupply.com</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="n"/>
-      <c r="E124" s="8" t="inlineStr">
-        <is>
-          <t>https://optimusdentalsupply.com/kerr-mixing-tips-small-yellow-48-pk/</t>
-        </is>
-      </c>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H124" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="64" customHeight="1">
-      <c r="A125" s="9" t="inlineStr">
+    <row r="136" ht="64" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>Genie VPS Magic Mix Stand Bulk Heavy Body 4/Pk
 SKU: 3120199  ·  Schein price: $518.89/unit</t>
         </is>
       </c>
-      <c r="B125" s="9" t="inlineStr">
+      <c r="B136" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>tdsc.com</t>
         </is>
       </c>
-      <c r="D125" s="10" t="n"/>
-      <c r="E125" s="12" t="inlineStr">
+      <c r="D136" s="6" t="n"/>
+      <c r="E136" s="8" t="inlineStr">
         <is>
           <t>https://www.tdsc.com/All-Categories/Dental-Supplies/Impression-Materials-%26-Accessories/Impression-Materials/Vinyl-Polysiloxane-%28VPS%29/Genie-VPS-Magic-Mix-Bulk-Kit/p/231255-4</t>
         </is>
       </c>
-      <c r="F125" s="10" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G125" s="9" t="inlineStr">
+      <c r="G136" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H125" s="10" t="inlineStr">
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="64" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="137" ht="64" customHeight="1">
+      <c r="A137" s="9" t="inlineStr">
         <is>
           <t>Genie VPS Magic Mix Stand Bulk Heavy Body 4/Pk
 SKU: 3120199  ·  Schein price: $518.89/unit</t>
         </is>
       </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="B137" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
+      <c r="C137" s="10" t="inlineStr">
         <is>
           <t>crazydentalprices.com</t>
         </is>
       </c>
-      <c r="D126" s="6" t="n"/>
-      <c r="E126" s="8" t="inlineStr">
+      <c r="D137" s="10" t="n"/>
+      <c r="E137" s="12" t="inlineStr">
         <is>
           <t>https://www.crazydentalprices.com/Supplies</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G137" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H126" s="6" t="inlineStr">
+      <c r="H137" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="64" customHeight="1">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>Genie VPS Magic Mix Stand Bulk Heavy Body 4/Pk
-SKU: 3120199  ·  Schein price: $518.89/unit</t>
-        </is>
-      </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C127" s="10" t="inlineStr">
-        <is>
-          <t>dcdental.com</t>
-        </is>
-      </c>
-      <c r="D127" s="10" t="n"/>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>https://www.dcdental.com/Genie-VPS-78815</t>
-        </is>
-      </c>
-      <c r="F127" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H127" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="64" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
+    <row r="138" ht="64" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>Genie Putty Rapid Set Berry 2x445 Gr
 SKU: 3122330  ·  Schein price: $121.60/unit</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B138" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>net32.com</t>
         </is>
       </c>
-      <c r="D128" s="6" t="n"/>
-      <c r="E128" s="8" t="inlineStr">
+      <c r="D138" s="6" t="n"/>
+      <c r="E138" s="8" t="inlineStr">
         <is>
           <t>https://www.net32.com/ec/genie-vps-impression-material-putty-rapid-set-d-73582</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G138" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H128" s="6" t="inlineStr">
+      <c r="H138" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="64" customHeight="1">
-      <c r="A129" s="9" t="inlineStr">
+    <row r="139" ht="64" customHeight="1">
+      <c r="A139" s="9" t="inlineStr">
         <is>
           <t>Genie Putty Rapid Set Berry 2x445 Gr
 SKU: 3122330  ·  Schein price: $121.60/unit</t>
         </is>
       </c>
-      <c r="B129" s="9" t="inlineStr">
+      <c r="B139" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C129" s="10" t="inlineStr">
-        <is>
-          <t>pattersondental.com</t>
-        </is>
-      </c>
-      <c r="D129" s="10" t="n"/>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/076660062</t>
-        </is>
-      </c>
-      <c r="F129" s="10" t="inlineStr">
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>scottsdental.com</t>
+        </is>
+      </c>
+      <c r="D139" s="10" t="n"/>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>https://www.scottsdental.com/genie.html</t>
+        </is>
+      </c>
+      <c r="F139" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G129" s="9" t="inlineStr">
+      <c r="G139" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H129" s="10" t="inlineStr">
+      <c r="H139" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="64" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
+    <row r="140" ht="64" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>Genie Putty Rapid Set Berry 2x445 Gr
 SKU: 3122330  ·  Schein price: $121.60/unit</t>
         </is>
       </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="B140" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>scottsdental.com</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="n"/>
-      <c r="E130" s="8" t="inlineStr">
-        <is>
-          <t>https://www.scottsdental.com/genie.html</t>
-        </is>
-      </c>
-      <c r="F130" s="6" t="inlineStr">
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>sultanhealthcare.com</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="n"/>
+      <c r="E140" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sultanhealthcare.com/restorative/genie-impression-material/</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G130" s="5" t="inlineStr">
+      <c r="G140" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H130" s="6" t="inlineStr">
+      <c r="H140" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="64" customHeight="1">
-      <c r="A131" s="9" t="inlineStr">
+    <row r="141" ht="64" customHeight="1">
+      <c r="A141" s="9" t="inlineStr">
         <is>
           <t>Genie Putty Rapid Set Berry 2x445 Gr
 SKU: 3122330  ·  Schein price: $121.60/unit</t>
         </is>
       </c>
-      <c r="B131" s="9" t="inlineStr">
+      <c r="B141" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C131" s="10" t="inlineStr">
-        <is>
-          <t>pattersondental.com</t>
-        </is>
-      </c>
-      <c r="D131" s="10" t="n"/>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/en-CA/Supplies/ItemDetail/076660062</t>
-        </is>
-      </c>
-      <c r="F131" s="10" t="inlineStr">
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>azdentall.com</t>
+        </is>
+      </c>
+      <c r="D141" s="10" t="n"/>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>https://azdentall.com/products/dental-impression-material-putty-hand-mix-normal-fast-set-heavy-body</t>
+        </is>
+      </c>
+      <c r="F141" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G131" s="9" t="inlineStr">
+      <c r="G141" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H131" s="10" t="inlineStr">
+      <c r="H141" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="64" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Genie Putty Rapid Set Berry 2x445 Gr
-SKU: 3122330  ·  Schein price: $121.60/unit</t>
-        </is>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>sultanhealthcare.com</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="n"/>
-      <c r="E132" s="8" t="inlineStr">
-        <is>
-          <t>https://www.sultanhealthcare.com/restorative/genie-impression-material/</t>
-        </is>
-      </c>
-      <c r="F132" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H132" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="64" customHeight="1">
-      <c r="A133" s="9" t="inlineStr">
-        <is>
-          <t>Genie Putty Rapid Set Berry 2x445 Gr
-SKU: 3122330  ·  Schein price: $121.60/unit</t>
-        </is>
-      </c>
-      <c r="B133" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
-        <is>
-          <t>sinclairdental.com</t>
-        </is>
-      </c>
-      <c r="D133" s="10" t="n"/>
-      <c r="E133" s="12" t="inlineStr">
-        <is>
-          <t>https://www.sinclairdental.com/Supplies/Impression-Materials/Vinyl-Polysiloxanes/Genie-Putty-Rapid-Set-2---300-Ml-Jars-2-Scoops/p/282sl01</t>
-        </is>
-      </c>
-      <c r="F133" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G133" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H133" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="64" customHeight="1">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>Genie Putty Rapid Set Berry 2x445 Gr
-SKU: 3122330  ·  Schein price: $121.60/unit</t>
-        </is>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>azdentall.com</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="n"/>
-      <c r="E134" s="8" t="inlineStr">
-        <is>
-          <t>https://azdentall.com/products/dental-impression-material-putty-hand-mix-normal-fast-set-heavy-body</t>
-        </is>
-      </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="64" customHeight="1">
-      <c r="A135" s="9" t="inlineStr">
+    <row r="142" ht="64" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>Speedclean For Autoclave 16oz/Bt
 SKU: 3865728  ·  Schein price: $35.99/unit</t>
         </is>
       </c>
-      <c r="B135" s="9" t="inlineStr">
+      <c r="B142" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="C142" s="6" t="inlineStr">
         <is>
           <t>frontierdental.com</t>
         </is>
       </c>
-      <c r="D135" s="10" t="n"/>
-      <c r="E135" s="12" t="inlineStr">
+      <c r="D142" s="6" t="n"/>
+      <c r="E142" s="8" t="inlineStr">
         <is>
           <t>https://www.frontierdental.com/us/en/product/speed-clean-autoclave-cleaner-1-pk-161997</t>
         </is>
       </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G135" s="9" t="inlineStr">
+      <c r="G142" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H135" s="10" t="inlineStr">
+      <c r="H142" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="64" customHeight="1">
-      <c r="A136" s="5" t="inlineStr">
+    <row r="143" ht="64" customHeight="1">
+      <c r="A143" s="9" t="inlineStr">
         <is>
           <t>Speedclean For Autoclave 16oz/Bt
 SKU: 3865728  ·  Schein price: $35.99/unit</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="B143" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>pattersondental.com</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="n"/>
-      <c r="E136" s="8" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/074876504</t>
-        </is>
-      </c>
-      <c r="F136" s="6" t="inlineStr">
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>dental.keystoneindustries.com</t>
+        </is>
+      </c>
+      <c r="D143" s="10" t="n"/>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>https://dental.keystoneindustries.com/product/autoclave-cleaner/</t>
+        </is>
+      </c>
+      <c r="F143" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G136" s="5" t="inlineStr">
+      <c r="G143" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="H143" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="64" customHeight="1">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>Speedclean For Autoclave 16oz/Bt
-SKU: 3865728  ·  Schein price: $35.99/unit</t>
-        </is>
-      </c>
-      <c r="B137" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
-        <is>
-          <t>dental.keystoneindustries.com</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="n"/>
-      <c r="E137" s="12" t="inlineStr">
-        <is>
-          <t>https://dental.keystoneindustries.com/product/autoclave-cleaner/</t>
-        </is>
-      </c>
-      <c r="F137" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G137" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H137" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="64" customHeight="1">
-      <c r="A138" s="5" t="inlineStr">
+    <row r="144" ht="64" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9736H-150 2/Pk
 SKU: 7013176  ·  Schein price: $66.58/unit</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="B144" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>pattersondental.com</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="n"/>
-      <c r="E138" s="8" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/Supplies/finishing-polishing-rotary-instruments/polishers/diamond-abrasives-for-porcelain/PIF_80270</t>
-        </is>
-      </c>
-      <c r="F138" s="6" t="inlineStr">
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>meisingerusa.com</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="8" t="inlineStr">
+        <is>
+          <t>https://meisingerusa.com/polishers-abrasives?page=3</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G138" s="5" t="inlineStr">
+      <c r="G144" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H138" s="6" t="inlineStr">
+      <c r="H144" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="64" customHeight="1">
-      <c r="A139" s="9" t="inlineStr">
+    <row r="145" ht="64" customHeight="1">
+      <c r="A145" s="9" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9736H-150 2/Pk
 SKU: 7013176  ·  Schein price: $66.58/unit</t>
         </is>
       </c>
-      <c r="B139" s="9" t="inlineStr">
+      <c r="B145" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C139" s="10" t="inlineStr">
-        <is>
-          <t>pattersondental.com</t>
-        </is>
-      </c>
-      <c r="D139" s="10" t="n"/>
-      <c r="E139" s="12" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/071399526</t>
-        </is>
-      </c>
-      <c r="F139" s="10" t="inlineStr">
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>ddsdentalsupplies.com</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="n"/>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>https://ddsdentalsupplies.com/9736g-150-hp-p-polisher-diamon/</t>
+        </is>
+      </c>
+      <c r="F145" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G139" s="9" t="inlineStr">
+      <c r="G145" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H139" s="10" t="inlineStr">
+      <c r="H145" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="64" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
+    <row r="146" ht="64" customHeight="1">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>Meisinger Polisher HP 9736H-150 2/Pk
 SKU: 7013176  ·  Schein price: $66.58/unit</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B146" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>meisingerusa.com</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="n"/>
-      <c r="E140" s="8" t="inlineStr">
-        <is>
-          <t>https://meisingerusa.com/polishers-abrasives?page=3</t>
-        </is>
-      </c>
-      <c r="F140" s="6" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>exceldentalshop.com</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="n"/>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>https://exceldentalshop.com/2174201</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G140" s="5" t="inlineStr">
+      <c r="G146" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H140" s="6" t="inlineStr">
+      <c r="H146" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="64" customHeight="1">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>Meisinger Polisher HP 9736H-150 2/Pk
-SKU: 7013176  ·  Schein price: $66.58/unit</t>
-        </is>
-      </c>
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
-        <is>
-          <t>midwestdental.com</t>
-        </is>
-      </c>
-      <c r="D141" s="10" t="n"/>
-      <c r="E141" s="12" t="inlineStr">
-        <is>
-          <t>https://midwestdental.com/product/view/18145</t>
-        </is>
-      </c>
-      <c r="F141" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G141" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H141" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="64" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>Meisinger Polisher HP 9736H-150 2/Pk
-SKU: 7013176  ·  Schein price: $66.58/unit</t>
-        </is>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>ddsdentalsupplies.com</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="n"/>
-      <c r="E142" s="8" t="inlineStr">
-        <is>
-          <t>https://ddsdentalsupplies.com/9736g-150-hp-p-polisher-diamon/</t>
-        </is>
-      </c>
-      <c r="F142" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="64" customHeight="1">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>Meisinger Polisher HP 9736H-150 2/Pk
-SKU: 7013176  ·  Schein price: $66.58/unit</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
-        <is>
-          <t>exceldentalshop.com</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="n"/>
-      <c r="E143" s="12" t="inlineStr">
-        <is>
-          <t>https://exceldentalshop.com/2174201</t>
-        </is>
-      </c>
-      <c r="F143" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G143" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H143" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="64" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
+    <row r="147" ht="64" customHeight="1">
+      <c r="A147" s="9" t="inlineStr">
         <is>
           <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
 SKU: 7120116  ·  Schein price: $13.35/unit</t>
         </is>
       </c>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="B147" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>midwestdental.com</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="n"/>
-      <c r="E144" s="8" t="inlineStr">
-        <is>
-          <t>https://midwestdental.com/toothbrushes/_item/imprint-tech-deep-clean-sens-tb-144cs</t>
-        </is>
-      </c>
-      <c r="F144" s="6" t="inlineStr">
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>sunstargum.com</t>
+        </is>
+      </c>
+      <c r="D147" s="10" t="n"/>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>https://www.sunstargum.com/us-en/products/toothbrushes/gum-technique-deep-clean-toothbrush.html</t>
+        </is>
+      </c>
+      <c r="F147" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G144" s="5" t="inlineStr">
+      <c r="G147" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H144" s="6" t="inlineStr">
+      <c r="H147" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="64" customHeight="1">
-      <c r="A145" s="9" t="inlineStr">
-        <is>
-          <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
-SKU: 7120116  ·  Schein price: $13.35/unit</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>darbydental.com</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="n"/>
-      <c r="E145" s="12" t="inlineStr">
-        <is>
-          <t>https://www.darbydental.com/8110122.html</t>
-        </is>
-      </c>
-      <c r="F145" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G145" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H145" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="64" customHeight="1">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>Gum Technique Deep Clean TB Soft Compact 12/Bx
-SKU: 7120116  ·  Schein price: $13.35/unit</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>sunstargum.com</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="n"/>
-      <c r="E146" s="8" t="inlineStr">
-        <is>
-          <t>https://www.sunstargum.com/us-en/products/toothbrushes/gum-technique-deep-clean-toothbrush.html</t>
-        </is>
-      </c>
-      <c r="F146" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H146" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="64" customHeight="1">
-      <c r="A147" s="9" t="inlineStr">
+    <row r="148" ht="64" customHeight="1">
+      <c r="A148" s="5" t="inlineStr">
         <is>
           <t>Premium Cotton Rolls #2 Non-Sterile 2000/Bx
 SKU: 8969286  ·  Schein price: $33.80/unit</t>
         </is>
       </c>
-      <c r="B147" s="9" t="inlineStr">
+      <c r="B148" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C147" s="10" t="inlineStr">
+      <c r="C148" s="6" t="inlineStr">
         <is>
           <t>graylinemedical.com</t>
         </is>
       </c>
-      <c r="D147" s="10" t="n"/>
-      <c r="E147" s="12" t="inlineStr">
+      <c r="D148" s="6" t="n"/>
+      <c r="E148" s="8" t="inlineStr">
         <is>
           <t>https://www.graylinemedical.com/products/henry-schein-cotton-roll-premium-hsi-medium-size-2-ns-0375-in-15-in-2000-bx-12-bx-ca8969286?variant=19330869755961</t>
         </is>
       </c>
-      <c r="F147" s="10" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G147" s="9" t="inlineStr">
+      <c r="G148" s="5" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H147" s="10" t="inlineStr">
+      <c r="H148" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="64" customHeight="1">
-      <c r="A148" s="5" t="inlineStr">
+    <row r="149" ht="64" customHeight="1">
+      <c r="A149" s="9" t="inlineStr">
         <is>
           <t>Premium Cotton Rolls #2 Non-Sterile 2000/Bx
 SKU: 8969286  ·  Schein price: $33.80/unit</t>
         </is>
       </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="B149" s="9" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
+      <c r="C149" s="10" t="inlineStr">
         <is>
           <t>graylinemedical.com</t>
         </is>
       </c>
-      <c r="D148" s="6" t="n"/>
-      <c r="E148" s="8" t="inlineStr">
+      <c r="D149" s="10" t="n"/>
+      <c r="E149" s="12" t="inlineStr">
         <is>
           <t>https://www.graylinemedical.com/products/henry-schein-cotton-roll-premium-hsi-medium-size-2-ns-0375-in-15-in-2000-bx-12-bx-ca8969286</t>
         </is>
       </c>
-      <c r="F148" s="6" t="inlineStr">
+      <c r="F149" s="10" t="inlineStr">
         <is>
           <t>NOT PRICED</t>
         </is>
       </c>
-      <c r="G148" s="5" t="inlineStr">
+      <c r="G149" s="9" t="inlineStr">
         <is>
           <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
         </is>
       </c>
-      <c r="H148" s="6" t="inlineStr">
+      <c r="H149" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="64" customHeight="1">
-      <c r="A149" s="9" t="inlineStr">
+    <row r="150" ht="64" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>Premium Cotton Rolls #2 Non-Sterile 2000/Bx
 SKU: 8969286  ·  Schein price: $33.80/unit</t>
         </is>
       </c>
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>darbydental.com</t>
-        </is>
-      </c>
-      <c r="D149" s="10" t="n"/>
-      <c r="E149" s="12" t="inlineStr">
-        <is>
-          <t>https://www.darbydental.com/3412020.html</t>
-        </is>
-      </c>
-      <c r="F149" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G149" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H149" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="64" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
-        <is>
-          <t>Premium Cotton Rolls #2 Non-Sterile 2000/Bx
-SKU: 8969286  ·  Schein price: $33.80/unit</t>
-        </is>
-      </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
           <t>(discovered listing — not priced)</t>
@@ -6709,8 +6734,8 @@
     <row r="152" ht="64" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk
-SKU: 7772551  ·  Schein price: $278.99/unit</t>
+          <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
+SKU: 1024081  ·  Schein price: $28.89/unit</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -6720,13 +6745,13 @@
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>pattersondental.com</t>
+          <t>orthazone.com</t>
         </is>
       </c>
       <c r="D152" s="6" t="n"/>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/Supplies/ItemDetail/071476704</t>
+          <t>https://www.orthazone.com/dental-treatment-accessories/dental-disposables-treatment-accessories/tray-covers-treatment-accessories</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
@@ -6748,8 +6773,8 @@
     <row r="153" ht="64" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk
-SKU: 7772551  ·  Schein price: $278.99/unit</t>
+          <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx
+SKU: 1126830  ·  Schein price: $16.15/unit</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -6759,13 +6784,13 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>pattersondental.com</t>
+          <t>afteractionmedical.com</t>
         </is>
       </c>
       <c r="D153" s="10" t="n"/>
       <c r="E153" s="12" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/Supplies/preventive-products/fluoride-varnishes/3m-clinpro-clear-fluoride-treatment/PIF_1108065</t>
+          <t>https://afteractionmedical.com/shop/criterion-n300-ultra-nitrile-exam-gloves/</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
@@ -6787,24 +6812,24 @@
     <row r="154" ht="64" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>3M Clinpro Clear Fluoride Trtm No Flavor 100/Pk
-SKU: 7772551  ·  Schein price: $278.99/unit</t>
+          <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx
+SKU: 1126830  ·  Schein price: $16.15/unit</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>(discovered listing — not priced)</t>
+          <t>Nitrile300 X-Small</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>darbydental.com</t>
+          <t>optimusdentalsupply.com</t>
         </is>
       </c>
       <c r="D154" s="6" t="n"/>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>https://www.darbydental.com/8900255.html</t>
+          <t>https://optimusdentalsupply.com/nitrile300-x-small/</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
@@ -6826,8 +6851,8 @@
     <row r="155" ht="64" customHeight="1">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>Tray Cover 8.5"x12.25" Aqua 1000/Ca
-SKU: 1024081  ·  Schein price: $28.89/unit</t>
+          <t>Criterion N300 Glove Ice Blue Nitrile M 300/Bx
+SKU: 1126831  ·  Schein price: $16.15/unit</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -6837,13 +6862,13 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>orthazone.com</t>
+          <t>afteractionmedical.com</t>
         </is>
       </c>
       <c r="D155" s="10" t="n"/>
       <c r="E155" s="12" t="inlineStr">
         <is>
-          <t>https://www.orthazone.com/dental-treatment-accessories/dental-disposables-treatment-accessories/tray-covers-treatment-accessories</t>
+          <t>https://afteractionmedical.com/shop/criterion-n300-ultra-nitrile-exam-gloves/</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
@@ -6865,8 +6890,8 @@
     <row r="156" ht="64" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>Criterion N300 Glove Ice Blue Nitrile S 300/Bx
-SKU: 1126830  ·  Schein price: $16.15/unit</t>
+          <t>Criterion N300 Glove Ice Blue Nitrile M 300/Bx
+SKU: 1126831  ·  Schein price: $16.15/unit</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -6876,13 +6901,13 @@
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>suprememed.com</t>
+          <t>mfidistribution.com</t>
         </is>
       </c>
       <c r="D156" s="6" t="n"/>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>https://www.suprememed.com/criterion-n300-nitrile-exam-gloves-standard-ice-blue-non-sterile/?attribute_pa_unit-of-measure-conf=bx300&amp;attribute_pa_size-conf=small</t>
+          <t>https://www.mfidistribution.com/criterion-n300-nitrile-exam-gloves-medium-standard</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
@@ -6910,18 +6935,18 @@
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>(discovered listing — not priced)</t>
+          <t>Criterion N300 Nitrile Exam Gloves – Standard</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>mfidistribution.com</t>
+          <t>suprememed.com</t>
         </is>
       </c>
       <c r="D157" s="10" t="n"/>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>https://www.mfidistribution.com/criterion-n300-nitrile-exam-gloves-medium-standard</t>
+          <t>https://www.suprememed.com/criterion-n300-nitrile-exam-gloves-standard-ice-blue-non-sterile/</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
@@ -6954,13 +6979,13 @@
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>pattersondental.com</t>
+          <t>meisingerusa.com</t>
         </is>
       </c>
       <c r="D158" s="6" t="n"/>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/en-CA/Supplies/finishing-polishing-rotary-instruments/polishers/diamond-flexible-polishers-for-porcelain-and-ceramics/PIF_53071</t>
+          <t>https://meisingerusa.com/polishers-abrasives?page=4</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
@@ -6999,7 +7024,7 @@
       <c r="D159" s="10" t="n"/>
       <c r="E159" s="12" t="inlineStr">
         <is>
-          <t>https://meisingerusa.com/polishers-abrasives?page=4</t>
+          <t>https://meisingerusa.com/9742g-040-hp-gr-o-polisher-diamond-impregnated-for-porcelain-green-orange-point-4mm-pre-polishing-coarse-hp-9742g-040-hp-gr-o</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -7032,13 +7057,13 @@
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>meisingerusa.com</t>
+          <t>dentalproductshopper.com</t>
         </is>
       </c>
       <c r="D160" s="6" t="n"/>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>https://meisingerusa.com/9742g-040-hp-gr-o-polisher-diamond-impregnated-for-porcelain-green-orange-point-4mm-pre-polishing-coarse-hp-9742g-040-hp-gr-o</t>
+          <t>https://www.dentalproductshopper.com/finishing-polishing/finishing-polishing-materials-strips/diamond-polisher-porcelain-blueorange-medium-hp-2pkg-pointed-9742m-040-mm-diameter</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
@@ -7060,8 +7085,8 @@
     <row r="161" ht="64" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>Meisinger Polisher HP 9742M-040 2/Pk
-SKU: 7013185  ·  Schein price: $47.55/unit</t>
+          <t>Sharps Cont Counter Balanced 3 Gal RD Ea
+SKU: 9872474  ·  Schein price: $17.42/unit</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -7071,13 +7096,13 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>dentalproductshopper.com</t>
+          <t>optimusdentalsupply.com</t>
         </is>
       </c>
       <c r="D161" s="10" t="n"/>
       <c r="E161" s="12" t="inlineStr">
         <is>
-          <t>https://www.dentalproductshopper.com/finishing-polishing/finishing-polishing-materials-strips/diamond-polisher-porcelain-blueorange-medium-hp-2pkg-pointed-9742m-040-mm-diameter</t>
+          <t>https://optimusdentalsupply.com/bd-sharps-collector/</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
@@ -7099,8 +7124,8 @@
     <row r="162" ht="64" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>Oral-B Glide Floss Deep Clean 4 meter Mint 72/Bx
-SKU: 3250498  ·  Schein price: $50.99/unit</t>
+          <t>Sharps Cont Counter Balanced 3 Gal RD Ea
+SKU: 9872474  ·  Schein price: $17.42/unit</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -7110,13 +7135,13 @@
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>orthazone.com</t>
+          <t>pstshop.com</t>
         </is>
       </c>
       <c r="D162" s="6" t="n"/>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>https://www.orthazone.com/209-fdt-glide-floss-pro-heah-original-4m-72cs-6265</t>
+          <t>https://www.pstshop.com/3-gallon-red-sharps-collector-10-case-305054/</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
@@ -7149,13 +7174,13 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>optimusdentalsupply.com</t>
+          <t>medexsupply.com</t>
         </is>
       </c>
       <c r="D163" s="10" t="n"/>
       <c r="E163" s="12" t="inlineStr">
         <is>
-          <t>https://optimusdentalsupply.com/bd-sharps-collector/</t>
+          <t>https://medexsupply.com/bd-sharps-collector-red-3-gallon/</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
@@ -7188,13 +7213,13 @@
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>pstshop.com</t>
+          <t>allfordentist.com</t>
         </is>
       </c>
       <c r="D164" s="6" t="n"/>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>https://www.pstshop.com/3-gallon-red-sharps-collector-10-case-305054/</t>
+          <t>https://www.allfordentist.com/multi-use-one-piece-sharps-container-5-4-quart-pearl-side-entry-prd-65195.html</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
@@ -7216,8 +7241,8 @@
     <row r="165" ht="64" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>Sharps Cont Counter Balanced 3 Gal RD Ea
-SKU: 9872474  ·  Schein price: $17.42/unit</t>
+          <t>ReSURGE Inst Cleaning Solution 33oz/Bt
+SKU: 3120114  ·  Schein price: $91.15/unit</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -7227,13 +7252,13 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>medexsupply.com</t>
+          <t>ddsdentalsupplies.com</t>
         </is>
       </c>
       <c r="D165" s="10" t="n"/>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>https://medexsupply.com/bd-sharps-collector-red-3-gallon/</t>
+          <t>https://ddsdentalsupplies.com/resurge-inst-cleaning-solution/</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
@@ -7255,8 +7280,8 @@
     <row r="166" ht="64" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>Sharps Cont Counter Balanced 3 Gal RD Ea
-SKU: 9872474  ·  Schein price: $17.42/unit</t>
+          <t>ReSURGE Inst Cleaning Solution 33oz/Bt
+SKU: 3120114  ·  Schein price: $91.15/unit</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
@@ -7266,13 +7291,13 @@
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>allfordentist.com</t>
+          <t>dentaladvisor.com</t>
         </is>
       </c>
       <c r="D166" s="6" t="n"/>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>https://www.allfordentist.com/multi-use-one-piece-sharps-container-5-4-quart-pearl-side-entry-prd-65195.html</t>
+          <t>https://dentaladvisor.com/clinical-evaluation/resurge/</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
@@ -7305,13 +7330,13 @@
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>pattersondental.com</t>
+          <t>offthecusp.com</t>
         </is>
       </c>
       <c r="D167" s="10" t="n"/>
       <c r="E167" s="12" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/en-CA/Supplies/ItemDetail/076649313</t>
+          <t>https://www.offthecusp.com/resurge-revolutionary-new-dental-instrument-cleaner/</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -7333,8 +7358,8 @@
     <row r="168" ht="64" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>ReSURGE Inst Cleaning Solution 33oz/Bt
-SKU: 3120114  ·  Schein price: $91.15/unit</t>
+          <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
+SKU: 1403081  ·  Schein price: $9.59/unit</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
@@ -7344,13 +7369,13 @@
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>ddsdentalsupplies.com</t>
+          <t>safcodental.com</t>
         </is>
       </c>
       <c r="D168" s="6" t="n"/>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>https://ddsdentalsupplies.com/resurge-inst-cleaning-solution/</t>
+          <t>https://www.safcodental.com/product/caviwipes-trade-2-0</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
@@ -7372,8 +7397,8 @@
     <row r="169" ht="64" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>ReSURGE Inst Cleaning Solution 33oz/Bt
-SKU: 3120114  ·  Schein price: $91.15/unit</t>
+          <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
+SKU: 1403081  ·  Schein price: $9.59/unit</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -7383,13 +7408,13 @@
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>dentaladvisor.com</t>
+          <t>skydentalsupply.com</t>
         </is>
       </c>
       <c r="D169" s="10" t="n"/>
       <c r="E169" s="12" t="inlineStr">
         <is>
-          <t>https://dentaladvisor.com/clinical-evaluation/resurge/</t>
+          <t>https://www.skydentalsupply.com/files/products/CaviWipes%202.0</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
@@ -7411,8 +7436,8 @@
     <row r="170" ht="64" customHeight="1">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>ReSURGE Inst Cleaning Solution 33oz/Bt
-SKU: 3120114  ·  Schein price: $91.15/unit</t>
+          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
+SKU: 3120212  ·  Schein price: $36.80/unit</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
@@ -7422,13 +7447,13 @@
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>offthecusp.com</t>
+          <t>supplydoc.com</t>
         </is>
       </c>
       <c r="D170" s="6" t="n"/>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>https://www.offthecusp.com/resurge-revolutionary-new-dental-instrument-cleaner/</t>
+          <t>https://supplydoc.com/products/genie-vps-50-ml</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
@@ -7450,8 +7475,8 @@
     <row r="171" ht="64" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
-SKU: 1403081  ·  Schein price: $9.59/unit</t>
+          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
+SKU: 3120212  ·  Schein price: $36.80/unit</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -7461,13 +7486,13 @@
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>safcodental.com</t>
+          <t>ddsdentalsupplies.com</t>
         </is>
       </c>
       <c r="D171" s="10" t="n"/>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>https://www.safcodental.com/product/caviwipes-trade-2-0</t>
+          <t>https://ddsdentalsupplies.com/sultan-genie-vps/</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
@@ -7489,8 +7514,8 @@
     <row r="172" ht="64" customHeight="1">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
-SKU: 1403081  ·  Schein price: $9.59/unit</t>
+          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
+SKU: 3120212  ·  Schein price: $36.80/unit</t>
         </is>
       </c>
       <c r="B172" s="5" t="inlineStr">
@@ -7500,13 +7525,13 @@
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>skydentalsupply.com</t>
+          <t>palmettodentalsupply.com</t>
         </is>
       </c>
       <c r="D172" s="6" t="n"/>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>https://www.skydentalsupply.com/files/products/CaviWipes%202.0</t>
+          <t>https://palmettodentalsupply.com/products/sultan-genie-vps-standard-set-light-body-50ml-2-pk</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
@@ -7528,8 +7553,8 @@
     <row r="173" ht="64" customHeight="1">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>CaviWipes 2.0 Wipes 6"x6.75" 160/Cn
-SKU: 1403081  ·  Schein price: $9.59/unit</t>
+          <t>Diamond FG Coarse 841G-012 5/Pk
+SKU: 7011085  ·  Schein price: $43.65/unit</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -7539,13 +7564,13 @@
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>pattersondental.com</t>
+          <t>surgimac.com</t>
         </is>
       </c>
       <c r="D173" s="10" t="n"/>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>https://www.pattersondental.com/Supplies/sterilization-disinfectant-cleaners/surface-disinfectant-wipes/caviwipes-2-0-surface-disinfectant-towelette/pif_1024450</t>
+          <t>https://surgimac.com/products/mark3-blue-streak-fg-862-010-coarse-flame-diamond-burs-5-pk</t>
         </is>
       </c>
       <c r="F173" s="10" t="inlineStr">
@@ -7567,8 +7592,8 @@
     <row r="174" ht="64" customHeight="1">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>Fuji II LC Capsules A3.5 48/Bx
-SKU: 3333468  ·  Schein price: $372.66/unit</t>
+          <t>Diamond FG Coarse 841G-012 5/Pk
+SKU: 7011085  ·  Schein price: $43.65/unit</t>
         </is>
       </c>
       <c r="B174" s="5" t="inlineStr">
@@ -7578,13 +7603,13 @@
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>supplyclinic.com</t>
+          <t>optimusdentalsupply.com</t>
         </is>
       </c>
       <c r="D174" s="6" t="n"/>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>https://www.supplyclinic.com/items/fuji-ii-lc-capsules-a3-5-48-bx-gc-america-425004</t>
+          <t>https://optimusdentalsupply.com/burs/kerr-nti-diamond-burs-c850l-012-coarse-fg-5-pk/</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
@@ -7606,8 +7631,8 @@
     <row r="175" ht="64" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>Fuji II LC Capsules A3.5 48/Bx
-SKU: 3333468  ·  Schein price: $372.66/unit</t>
+          <t>Diamond FG Coarse 841G-012 5/Pk
+SKU: 7011085  ·  Schein price: $43.65/unit</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -7617,13 +7642,13 @@
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>net32.com</t>
+          <t>primedentalsupply.com</t>
         </is>
       </c>
       <c r="D175" s="10" t="n"/>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>https://www.net32.com/ec/gc-fuji-ii-lc-a35-capsules-48-d-130428</t>
+          <t>https://www.primedentalsupply.com/fg835c-diamond-bur-coarse-5-brpk-kerr-dental-00450449-bd5</t>
         </is>
       </c>
       <c r="F175" s="10" t="inlineStr">
@@ -7645,8 +7670,8 @@
     <row r="176" ht="64" customHeight="1">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>Fuji II LC Capsules A3.5 48/Bx
-SKU: 3333468  ·  Schein price: $372.66/unit</t>
+          <t>Diamond FG Coarse 841G-012 5/Pk
+SKU: 7011085  ·  Schein price: $43.65/unit</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">
@@ -7656,13 +7681,13 @@
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>crazydentalprices.com</t>
+          <t>kerrdental.com</t>
         </is>
       </c>
       <c r="D176" s="6" t="n"/>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>https://www.crazydentalprices.com/Fuji-II-LC-Capsules-425004_2</t>
+          <t>https://www.kerrdental.com/en-us/rotary</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
@@ -7676,513 +7701,6 @@
         </is>
       </c>
       <c r="H176" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="64" customHeight="1">
-      <c r="A177" s="9" t="inlineStr">
-        <is>
-          <t>Fuji II LC Capsules A3.5 48/Bx
-SKU: 3333468  ·  Schein price: $372.66/unit</t>
-        </is>
-      </c>
-      <c r="B177" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C177" s="10" t="inlineStr">
-        <is>
-          <t>frontierdental.com</t>
-        </is>
-      </c>
-      <c r="D177" s="10" t="n"/>
-      <c r="E177" s="12" t="inlineStr">
-        <is>
-          <t>https://frontierdental.com/us/en/product/fuji-ii-lc-glass-ionomer-restorative-light-cure-capsules-refill-0-1-ml-a3-5-48-pk-36413?bp=ZnJvbnRpZXJkZW50YWw%3D&amp;ctr=VVM%3D</t>
-        </is>
-      </c>
-      <c r="F177" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G177" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H177" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="64" customHeight="1">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>Fuji II LC Capsules A3 48/Bx
-SKU: 3333466  ·  Schein price: $372.66/unit</t>
-        </is>
-      </c>
-      <c r="B178" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>supplyclinic.com</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="n"/>
-      <c r="E178" s="8" t="inlineStr">
-        <is>
-          <t>https://www.supplyclinic.com/items/fuji-ii-lc-capsules-a3-48-bx-gc-america-425003?kw=&amp;cpn=23795785166</t>
-        </is>
-      </c>
-      <c r="F178" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G178" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H178" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="64" customHeight="1">
-      <c r="A179" s="9" t="inlineStr">
-        <is>
-          <t>Fuji II LC Capsules A3 48/Bx
-SKU: 3333466  ·  Schein price: $372.66/unit</t>
-        </is>
-      </c>
-      <c r="B179" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C179" s="10" t="inlineStr">
-        <is>
-          <t>net32.com</t>
-        </is>
-      </c>
-      <c r="D179" s="10" t="n"/>
-      <c r="E179" s="12" t="inlineStr">
-        <is>
-          <t>https://www.net32.com/ec/gc-fuji-ii-lc-a3-capsules-50-d-20149</t>
-        </is>
-      </c>
-      <c r="F179" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G179" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H179" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="64" customHeight="1">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>Fuji II LC Capsules A3 48/Bx
-SKU: 3333466  ·  Schein price: $372.66/unit</t>
-        </is>
-      </c>
-      <c r="B180" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C180" s="6" t="inlineStr">
-        <is>
-          <t>frontierdental.com</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="n"/>
-      <c r="E180" s="8" t="inlineStr">
-        <is>
-          <t>https://frontierdental.com/us/en/product/fuji-ii-lc-glass-ionomer-restorative-light-cure-capsules-refill-0-1-ml-a3-48-pk-36596?bp=ZnJvbnRpZXJkZW50YWw%3D&amp;ctr=VVM%3D</t>
-        </is>
-      </c>
-      <c r="F180" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G180" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H180" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="64" customHeight="1">
-      <c r="A181" s="9" t="inlineStr">
-        <is>
-          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
-SKU: 3120212  ·  Schein price: $36.80/unit</t>
-        </is>
-      </c>
-      <c r="B181" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C181" s="10" t="inlineStr">
-        <is>
-          <t>supplydoc.com</t>
-        </is>
-      </c>
-      <c r="D181" s="10" t="n"/>
-      <c r="E181" s="12" t="inlineStr">
-        <is>
-          <t>https://supplydoc.com/products/genie-vps-50-ml</t>
-        </is>
-      </c>
-      <c r="F181" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G181" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H181" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="64" customHeight="1">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
-SKU: 3120212  ·  Schein price: $36.80/unit</t>
-        </is>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>ddsdentalsupplies.com</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="n"/>
-      <c r="E182" s="8" t="inlineStr">
-        <is>
-          <t>https://ddsdentalsupplies.com/sultan-genie-vps/</t>
-        </is>
-      </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G182" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H182" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="64" customHeight="1">
-      <c r="A183" s="9" t="inlineStr">
-        <is>
-          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
-SKU: 3120212  ·  Schein price: $36.80/unit</t>
-        </is>
-      </c>
-      <c r="B183" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C183" s="10" t="inlineStr">
-        <is>
-          <t>pattersondental.com</t>
-        </is>
-      </c>
-      <c r="D183" s="10" t="n"/>
-      <c r="E183" s="12" t="inlineStr">
-        <is>
-          <t>https://www.pattersondental.com/en-CA/Supplies/ItemDetail/076660062</t>
-        </is>
-      </c>
-      <c r="F183" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G183" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H183" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="64" customHeight="1">
-      <c r="A184" s="5" t="inlineStr">
-        <is>
-          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
-SKU: 3120212  ·  Schein price: $36.80/unit</t>
-        </is>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C184" s="6" t="inlineStr">
-        <is>
-          <t>palmettodentalsupply.com</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="n"/>
-      <c r="E184" s="8" t="inlineStr">
-        <is>
-          <t>https://palmettodentalsupply.com/products/sultan-genie-vps-standard-set-light-body-50ml-2-pk</t>
-        </is>
-      </c>
-      <c r="F184" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H184" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="64" customHeight="1">
-      <c r="A185" s="9" t="inlineStr">
-        <is>
-          <t>Genie VPS Rapid Set 50mL XLight Body 2/Pk
-SKU: 3120212  ·  Schein price: $36.80/unit</t>
-        </is>
-      </c>
-      <c r="B185" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C185" s="10" t="inlineStr">
-        <is>
-          <t>sinclairdental.com</t>
-        </is>
-      </c>
-      <c r="D185" s="10" t="n"/>
-      <c r="E185" s="12" t="inlineStr">
-        <is>
-          <t>https://www.sinclairdental.com/en/Supplies/Impression-Materials/Vinyl-Polysiloxanes/Genie-Xtra-Light-Body-Rapid-Set-%28New%29-2-50ml-Cartridges-%2526-6-Tips-%28Berry%29/p/281sl14/</t>
-        </is>
-      </c>
-      <c r="F185" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G185" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H185" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="64" customHeight="1">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>Diamond FG Coarse 841G-012 5/Pk
-SKU: 7011085  ·  Schein price: $43.65/unit</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>surgimac.com</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="n"/>
-      <c r="E186" s="8" t="inlineStr">
-        <is>
-          <t>https://surgimac.com/products/mark3-blue-streak-fg-862-010-coarse-flame-diamond-burs-5-pk</t>
-        </is>
-      </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H186" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="64" customHeight="1">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t>Diamond FG Coarse 841G-012 5/Pk
-SKU: 7011085  ·  Schein price: $43.65/unit</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C187" s="10" t="inlineStr">
-        <is>
-          <t>optimusdentalsupply.com</t>
-        </is>
-      </c>
-      <c r="D187" s="10" t="n"/>
-      <c r="E187" s="12" t="inlineStr">
-        <is>
-          <t>https://optimusdentalsupply.com/burs/kerr-nti-diamond-burs-c850l-012-coarse-fg-5-pk/</t>
-        </is>
-      </c>
-      <c r="F187" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G187" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H187" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="64" customHeight="1">
-      <c r="A188" s="5" t="inlineStr">
-        <is>
-          <t>Diamond FG Coarse 841G-012 5/Pk
-SKU: 7011085  ·  Schein price: $43.65/unit</t>
-        </is>
-      </c>
-      <c r="B188" s="5" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>primedentalsupply.com</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="n"/>
-      <c r="E188" s="8" t="inlineStr">
-        <is>
-          <t>https://www.primedentalsupply.com/fg835c-diamond-bur-coarse-5-brpk-kerr-dental-00450449-bd5</t>
-        </is>
-      </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G188" s="5" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H188" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="64" customHeight="1">
-      <c r="A189" s="9" t="inlineStr">
-        <is>
-          <t>Diamond FG Coarse 841G-012 5/Pk
-SKU: 7011085  ·  Schein price: $43.65/unit</t>
-        </is>
-      </c>
-      <c r="B189" s="9" t="inlineStr">
-        <is>
-          <t>(discovered listing — not priced)</t>
-        </is>
-      </c>
-      <c r="C189" s="10" t="inlineStr">
-        <is>
-          <t>kerrdental.com</t>
-        </is>
-      </c>
-      <c r="D189" s="10" t="n"/>
-      <c r="E189" s="12" t="inlineStr">
-        <is>
-          <t>https://www.kerrdental.com/en-us/rotary</t>
-        </is>
-      </c>
-      <c r="F189" s="10" t="inlineStr">
-        <is>
-          <t>NOT PRICED</t>
-        </is>
-      </c>
-      <c r="G189" s="9" t="inlineStr">
-        <is>
-          <t>DISCOVERED — found during search but not priced this run (per-item scrape cap reached). Open the link to check the price, or raise SCRAPE_CAP_PER_ITEM to price more per item.</t>
-        </is>
-      </c>
-      <c r="H189" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8367,19 +7885,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E174" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E175" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E176" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E177" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E178" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E179" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E180" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E181" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E182" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E184" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E185" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E186" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E187" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E188" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E189" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
